--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-UNIT-11</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>TC-02</t>
+          <t>TC-UNIT-12</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>TC-03</t>
+          <t>TC-UNIT-20</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>TC-04</t>
+          <t>TC-UNIT-26</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>TC-05</t>
+          <t>TC-UNIT-42</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>TC-06</t>
+          <t>TC-UNIT-43</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>TC-07</t>
+          <t>TC-E2E-08</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-UNIT-01</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>TC-02</t>
+          <t>TC-UNIT-02</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>TC-03</t>
+          <t>TC-UNIT-09</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>TC-04</t>
+          <t>TC-UNIT-10</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>TC-05</t>
+          <t>TC-UNIT-13</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>TC-06</t>
+          <t>TC-UNIT-14</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>TC-07</t>
+          <t>TC-UNIT-33</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>TC-08</t>
+          <t>TC-E2E-03</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>TC-09</t>
+          <t>TC-E2E-04</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>TC-10</t>
+          <t>TC-E2E-05</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>TC-11</t>
+          <t>TC-E2E-11</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-UNIT-03</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>TC-02</t>
+          <t>TC-UNIT-35</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>TC-03</t>
+          <t>TC-E2E-01</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>TC-04</t>
+          <t>TC-E2E-02</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-UNIT-04</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>TC-02</t>
+          <t>TC-UNIT-05</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>TC-03</t>
+          <t>TC-UNIT-27</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>TC-04</t>
+          <t>TC-UNIT-28</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>TC-05</t>
+          <t>TC-UNIT-29</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>TC-06</t>
+          <t>TC-UNIT-30</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>TC-07</t>
+          <t>TC-UNIT-31</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>TC-08</t>
+          <t>TC-UNIT-32</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>TC-09</t>
+          <t>TC-UNIT-36</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>TC-10</t>
+          <t>TC-UNIT-37</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>TC-11</t>
+          <t>TC-UNIT-38</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>TC-12</t>
+          <t>TC-UNIT-39</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>TC-13</t>
+          <t>TC-UNIT-40</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>TC-14</t>
+          <t>TC-UNIT-41</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>TC-15</t>
+          <t>TC-UNIT-46</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-UNIT-06</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>TC-02</t>
+          <t>TC-UNIT-07</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>TC-03</t>
+          <t>TC-UNIT-15</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>TC-04</t>
+          <t>TC-UNIT-16</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>TC-05</t>
+          <t>TC-UNIT-17</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>TC-06</t>
+          <t>TC-UNIT-18</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>TC-07</t>
+          <t>TC-UNIT-19</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>TC-08</t>
+          <t>TC-UNIT-21</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>TC-09</t>
+          <t>TC-UNIT-22</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>TC-10</t>
+          <t>TC-UNIT-23</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>TC-11</t>
+          <t>TC-UNIT-24</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>TC-12</t>
+          <t>TC-UNIT-25</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>TC-13</t>
+          <t>TC-UNIT-44</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>TC-14</t>
+          <t>TC-UNIT-45</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>TC-15</t>
+          <t>TC-E2E-06</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>TC-16</t>
+          <t>TC-E2E-07</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>TC-17</t>
+          <t>TC-E2E-12</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-UNIT-08</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>TC-02</t>
+          <t>TC-UNIT-34</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>TC-03</t>
+          <t>TC-E2E-09</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>TC-04</t>
+          <t>TC-E2E-10</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-SPRINT-01</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>TC-02</t>
+          <t>TC-SPRINT-02</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>TC-03</t>
+          <t>TC-SPRINT-03</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>TC-04</t>
+          <t>TC-SPRINT-04</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>TC-05</t>
+          <t>TC-SPRINT-05</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>TC-06</t>
+          <t>TC-SPRINT-06</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>TC-07</t>
+          <t>TC-SPRINT-07</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3010,10 +3010,470 @@
         </is>
       </c>
     </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🖥️ Application Uptime &amp; Sprint Pipeline Quality Gates</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="36" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>🖥️ Application Uptime &amp; Sprint Pipeline Quality Gates</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>TC-UPTIME-01</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Backend &amp; Frontend Port Health Check</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Server Health Monitoring Service</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>The server health helper will detect when backend port 8000 or frontend port 5173 is offline.</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified server_health.servers_healthy() reports accurate up/down status for both application ports.</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>🖥️ Application Uptime &amp; Sprint Pipeline Quality Gates</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>TC-UPTIME-02</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Automatic Server Auto-Start Before Tests</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Pre-Test Server Recovery Engine</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>When browser tests run and servers are down, the tester agent will automatically launch backend and frontend and wait until both respond.</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified ensure_servers_running() starts missing services and browser tests proceed without connection refused errors.</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>🖥️ Application Uptime &amp; Sprint Pipeline Quality Gates</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>TC-UPTIME-03</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Watchdog Supervisor Auto-Restart Loop</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Agent Watchdog Self-Healing Supervisor</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>The watchdog process will poll every 15 seconds and restart crashed backend, frontend, or sprint watcher processes.</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified agent_watchdog.py restarts offline services without manual user intervention.</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="36" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>🖥️ Application Uptime &amp; Sprint Pipeline Quality Gates</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>TC-SPRINT-08</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Watcher Server Gate Before Quality Gate</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Pipeline Pre-Test Server Mandate</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>Before running the full pytest suite for a Plane task, the sprint watcher will verify application servers are running.</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified sprint_watcher_agent calls ensure_servers_running() before invoking tester_agent for unit and browser tests.</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>🖥️ Application Uptime &amp; Sprint Pipeline Quality Gates</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>TC-SPRINT-09</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Pickup Groups Exclude Backlog Tasks</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Sprint Task Pickup Filter Policy</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>The sprint watcher will only auto-pick tasks in unstarted, todo, or triaged states and will not pick backlog items.</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified AGENT_PICKUP_GROUPS excludes backlog and unit test test_pickup_groups_excludes_backlog passes.</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📋 Sprint Task: Remove Unwanted Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>📋 Sprint Task: Remove Unwanted Content</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>TC-TASK-PLANE-DE-SMOKE</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard smoke after sprint task: Remove Unwanted Content</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Sprint Task Regression Smoke Test</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>After implementing the sprint task 'Remove Unwanted Content', the main dashboard loads with KPI cards and global header controls working.</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Successfully verified in browser: After implementing the sprint task 'Remove Unwanted Content', the main dashboard loads with KPI cards and global header </t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>📋 Sprint Task: Remove Unwanted Content</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>TC-TASK-PLANE-DE-HIDE-UI</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Unwanted dashboard widgets remain hidden</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>Remove Unwanted Content Task Verification</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>The dashboard will not show Copilot Search Fixes, Warehouse Level Statistics, or Agent Task Activity Tracker widgets.</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified in browser: The dashboard will not show Copilot Search Fixes, Warehouse Level Statistics, or Agent Task Activity Tracker widgets.</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>📋 Sprint Task: Remove Unwanted Content</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>TC-TASK-PLANE-DE-COPILOT</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>AI Data Copilot accepts prompts and shows results</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>AI Data Copilot Sprint Task Verification</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified in browser: The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>📋 Sprint Task: Remove Unwanted Content</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>TC-TASK-PLANE-DE-TABLE</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse sales table loads with data rows</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse Analytics Table Verification</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified in browser: Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>📋 Sprint Task: Remove Unwanted Content</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>TC-TASK-PLANE-DE-HEADER</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Global header controls and clear filter work</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Header Controls Sprint Task Verification</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified in browser: Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>📋 Sprint Task: Remove Unwanted Content</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>TC-TASK-PLANE-DE-AGENTS</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Agent status telemetry visible in sidebar</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>Agent Fleet Monitoring Verification</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified in browser: The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>📋 Sprint Task: Remove Unwanted Content</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>TC-TASK-PLANE-DE-UPTIME</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Application servers respond for browser testing</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Application Uptime Verification</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified in browser: The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A80:G80"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A2:G2"/>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,11 +51,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00166534"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,14 +82,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
         <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +153,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -591,12 +606,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified agent status telemetry reports all 6 agent fleet processes active in RUNNING state.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -628,12 +643,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified system health check confirms healthy operational status and active database pool.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -665,12 +680,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified data router operational status and confirmed data service readiness.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -702,12 +717,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified system metadata confirming platform title AgenticOps AI and version 1.0.0.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -739,12 +754,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified parameter-driven query routing executes seamlessly against requested target database.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -776,12 +791,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified DEV database connection retrieves active warehouse inventory records.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -813,12 +828,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified switching database reloads KPI cards, bar charts, and data tables with matching database metrics.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -857,12 +872,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified AI Copilot historical date query bypasses date constraints and retrieves complete warehouse statistics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -894,12 +909,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified AI Copilot search without date filter returns summary finding statements and metric totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -931,12 +946,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified server-side date override executes full-dataset analysis across all historical dates.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -968,12 +983,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot generates clear summary answer detailing invoice counts, cases built, and scratch quantities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1020,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified prompt '58 warehouse overview' extracts Warehouse 58 and filters chart data strictly to facility 58.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1057,12 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified query 'high scratch quantity' detects scratch intent and returns scratch item totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1094,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot search payload contains summary answers, applied filters, metrics, and chart data.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1131,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified submitting Copilot prompt renders summary card with matching metric counts.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1168,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot prompt updates Copilot chart, KPI cards, main bar chart, scatter plot, anomaly panel, and table.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1205,12 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified clicking clear button resets Copilot mode, hides banner, and restores baseline dashboard widgets.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1242,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified asking 'high scratch quantity' sets scratch filter and reloads table showing scratch rows.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1286,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified summary metrics return card data matching Cases Built, Order Qty, Invoices, and Active Warehouses.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1323,12 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified KPI metrics engine accepts all filter parameters and returns updated totals specific to criteria.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1360,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified dashboard loads cleanly, executes data requests, and renders 6 executive KPI cards with live values.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1397,12 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified submitting order date '2026-07-17' reloads KPI cards, bar chart, scatter plot, and data table with date records.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1441,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart returns data array containing warehouse labels and cases built values for active facilities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1478,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified scatter plot returns data array containing numeric order quantity and cases built coordinate points.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1515,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified analytics column service categorizes columns into numeric and categorical feature lists.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1552,12 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Random Forest model training fits features and returns accuracy evaluation metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1589,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Logistic Regression training fits features and returns accuracy performance metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1626,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified training both classifiers executes successfully and returns comparative performance metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1663,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified requesting invalid target column returns clear validation error message.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1700,12 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified querying model results before training indicates no models have been trained yet.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1737,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart calculation engine returns aggregated cases built totals for each active warehouse facility.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1774,12 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting custom metric calculates average metric values for each warehouse facility.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1811,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified invalid column parameter gracefully falls back to default warehouse aggregation without failure.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1848,12 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified scatter plot extracts valid numeric coordinate pairs for visualization.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1885,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified heatmap service calculates correlation matrix containing x, y, and correlation scores.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1922,12 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified distribution service calculates histogram bins with range labels and row counts.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1959,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified charts service reads SQL summary totals and returns aligned Cases Built numbers for facilities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1988,12 +2003,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified warehouse statistics service retrieves line items array, total count, and pagination details.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2040,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified querying warehouse statistics without date filter returns full dataset items across all dates.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2077,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified navigation bar renders AgenticOps AI branding logo and top-level navigation links.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2114,12 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sales analytics component renders table headers, pagination controls, and filter inputs.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2151,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified inventory risk component exports functional component with risk forecasting logic.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2188,12 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified warehouse service connects to PostgreSQL database and returns inventory line items and totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2225,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified data table component processes external filter properties and dynamically sets warehouse and scratch filters.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2247,12 +2262,12 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sample data service returns structured payload containing 100 row objects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2299,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified requesting 50 sample rows returns payload containing exactly 50 row objects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2336,12 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified dataset summary service calculates summary details containing row count and column statistics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2373,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified uploading non-CSV file reports validation error rejecting invalid file type.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2395,12 +2410,12 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified uploading valid CSV file parses rows, updates active dataset, and confirms record count.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2447,12 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified order date is formatted to YYYYMMDD and filtered in query returning matching order date rows.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2469,12 +2484,12 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified returned line items contain required keys: whs_num, batch_id, oerdte, cases_bld_stg, orgnl_ordr_qty_stg, and whs_scrtch_qty_stg.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2506,12 +2521,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified checking 'Filter Scratches' reloads data table displaying exclusively line items with scratch quantity &gt; 0.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2558,12 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting 'Whse 58' from dropdown reloads table displaying exclusively rows matching Warehouse 58.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2595,12 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified clicking pagination button fetches page 2, updating row count indicator to loaded items.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2639,12 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified anomaly scanner retrieves risk alert objects containing severity, title, message, and warehouse location.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2676,12 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified anomaly scanner outputs risk alerts with severity ratings (Critical, Warning, Info) and facility locations.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2713,12 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Anomaly Alert Panel renders risk cards with colored severity badges (Critical Red, Warning Amber, Info Cyan).</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2750,12 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified clicking 'Filter Table' on anomaly card updates table filters and displays matching Warehouse line items.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2794,12 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified workspace listing retrieves workspace array containing agentbuilder and project IDs.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2831,12 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting All Projects aggregates tasks from AgenticOps AI, AAD, and agentbuilder projects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2868,12 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified task objects contain exact project_name tags ('AgenticOps AI - Enterprise Control Plane', 'AI Analytics Dashboard').</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2905,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified SprintBoard.jsx renders 4 distinct Kanban columns for Backlog, To Do, In Progress, and Completed.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2927,12 +2942,12 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified changing workspace or project scope reloads sprint board tasks and updates project badges.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2964,12 +2979,12 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified AgentMonitor.jsx and AgentTaskActivityTracker.jsx render running status table and live execution stream.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3016,12 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Playwright browser inspects select elements and confirms dark background colors (rgb(30, 41, 59)) with crisp option styling.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3045,12 +3060,12 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified server_health.servers_healthy() reports accurate up/down status for both application ports.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3097,12 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified ensure_servers_running() starts missing services and browser tests proceed without connection refused errors.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3134,12 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified agent_watchdog.py restarts offline services without manual user intervention.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3171,12 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sprint_watcher_agent calls ensure_servers_running() before invoking tester_agent for unit and browser tests.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3193,36 +3208,36 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified AGENT_PICKUP_GROUPS excludes backlog and unit test test_pickup_groups_excludes_backlog passes.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  📋 Sprint Task: Remove Unwanted Content</t>
+          <t xml:space="preserve">  📋 Sprint Task: Data Analytics</t>
         </is>
       </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Remove Unwanted Content</t>
+          <t>📋 Sprint Task: Data Analytics</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-PLANE-DE-SMOKE</t>
+          <t>TC-TASK-1150CF09-SMOKE</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Dashboard smoke after sprint task: Remove Unwanted Content</t>
+          <t>Dashboard smoke after sprint task: Data Analytics</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3232,250 +3247,669 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>After implementing the sprint task 'Remove Unwanted Content', the main dashboard loads with KPI cards and global header controls working.</t>
+          <t>After implementing the sprint task 'Data Analytics', the main dashboard loads with KPI cards and global header controls working.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Successfully verified in browser: After implementing the sprint task 'Remove Unwanted Content', the main dashboard loads with KPI cards and global header </t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Remove Unwanted Content</t>
+          <t>📋 Sprint Task: Data Analytics</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-PLANE-DE-HIDE-UI</t>
+          <t>TC-TASK-1150CF09-COPILOT</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Unwanted dashboard widgets remain hidden</t>
+          <t>AI Data Copilot accepts prompts and shows results</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Remove Unwanted Content Task Verification</t>
+          <t>AI Data Copilot Sprint Task Verification</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>The dashboard will not show Copilot Search Fixes, Warehouse Level Statistics, or Agent Task Activity Tracker widgets.</t>
+          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: The dashboard will not show Copilot Search Fixes, Warehouse Level Statistics, or Agent Task Activity Tracker widgets.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Remove Unwanted Content</t>
+          <t>📋 Sprint Task: Data Analytics</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-PLANE-DE-COPILOT</t>
+          <t>TC-TASK-1150CF09-TABLE</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>AI Data Copilot accepts prompts and shows results</t>
+          <t>Warehouse sales table loads with data rows</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>AI Data Copilot Sprint Task Verification</t>
+          <t>Warehouse Analytics Table Verification</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
+          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Remove Unwanted Content</t>
+          <t>📋 Sprint Task: Data Analytics</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-PLANE-DE-TABLE</t>
+          <t>TC-TASK-1150CF09-HEADER</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Warehouse sales table loads with data rows</t>
+          <t>Global header controls and clear filter work</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Warehouse Analytics Table Verification</t>
+          <t>Header Controls Sprint Task Verification</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Remove Unwanted Content</t>
+          <t>📋 Sprint Task: Data Analytics</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-PLANE-DE-HEADER</t>
+          <t>TC-TASK-1150CF09-AGENTS</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Global header controls and clear filter work</t>
+          <t>Agent status telemetry visible in sidebar</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Header Controls Sprint Task Verification</t>
+          <t>Agent Fleet Monitoring Verification</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
+          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Remove Unwanted Content</t>
+          <t>📋 Sprint Task: Data Analytics</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-PLANE-DE-AGENTS</t>
+          <t>TC-TASK-1150CF09-UPTIME</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Agent status telemetry visible in sidebar</t>
+          <t>Application servers respond for browser testing</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Agent Fleet Monitoring Verification</t>
+          <t>Application Uptime Verification</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-01</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard Date+DB Submit KPI Alignment</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Comprehensive Dashboard Filter Engine</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="36" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>📋 Sprint Task: Remove Unwanted Content</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>TC-TASK-PLANE-DE-UPTIME</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>Application servers respond for browser testing</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>Application Uptime Verification</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified in browser: The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-02</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse Filter Bar Chart Calculation</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse Bar Chart Calculation Verifier</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-03</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Table Summary Cards API Alignment</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Warehouse Table Summary Calculation Engine</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-04</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Search Without Date Parameter</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Date-Agnostic Search Engine</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-05</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Analytics Screen ML Controls</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Analytics Module Browser Smoke Test</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified Analytics page loads with model training controls visible.</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-06</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Board All Dropdowns + Columns</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Board Comprehensive Module Test</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="36" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-07</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Agent Monitor Fleet Screen</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Agent Monitor Module Browser Test</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="36" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-08</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Screen Load</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Module Browser Test</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-09</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Full Filter Chain Scratch Submit</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Scratch Filter Propagation Engine</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-10</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>Single Warehouse KPI vs Bar Chart Parity</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Cross-Widget Calculation Parity Engine</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-11</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Global Submit Uses Date Parameter</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Global Header Filter Engine</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-12</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Two Warehouses Different KPI</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Warehouse Calculation Engine</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>Discover two warehouses from API; Copilot queries must return different Cases Built totals per facility.</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>tests\browser\test_comprehensive_module_suite.py:353: in test_copilot_two_warehouses_different_kpi
+    assert_cases_aligned(cases_a, exp_a)
+tests\browser\calculation_verifier.py:114: in assert_cases_aligned
+    assert diff &lt;= allowed, (
+E   AssertionError: Cases built mismatch: API=0 UI=8,500 (diff=8,500)</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="A61:G61"/>
     <mergeCell ref="A74:G74"/>
     <mergeCell ref="A80:G80"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A87:G87"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A10:G10"/>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -51,13 +51,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00166534"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00166534"/>
+      <color rgb="00991B1B"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -82,8 +82,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,8 +94,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -606,12 +606,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified agent status telemetry reports all 6 agent fleet processes active in RUNNING state.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -643,12 +643,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified system health check confirms healthy operational status and active database pool.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified data router operational status and confirmed data service readiness.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified system metadata confirming platform title AgenticOps AI and version 1.0.0.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified parameter-driven query routing executes seamlessly against requested target database.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified DEV database connection retrieves active warehouse inventory records.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified switching database reloads KPI cards, bar charts, and data tables with matching database metrics.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AI Copilot historical date query bypasses date constraints and retrieves complete warehouse statistics.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AI Copilot search without date filter returns summary finding statements and metric totals.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified server-side date override executes full-dataset analysis across all historical dates.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot generates clear summary answer detailing invoice counts, cases built, and scratch quantities.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified prompt '58 warehouse overview' extracts Warehouse 58 and filters chart data strictly to facility 58.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified query 'high scratch quantity' detects scratch intent and returns scratch item totals.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot search payload contains summary answers, applied filters, metrics, and chart data.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified submitting Copilot prompt renders summary card with matching metric counts.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot prompt updates Copilot chart, KPI cards, main bar chart, scatter plot, anomaly panel, and table.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking clear button resets Copilot mode, hides banner, and restores baseline dashboard widgets.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified asking 'high scratch quantity' sets scratch filter and reloads table showing scratch rows.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified summary metrics return card data matching Cases Built, Order Qty, Invoices, and Active Warehouses.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified KPI metrics engine accepts all filter parameters and returns updated totals specific to criteria.</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified dashboard loads cleanly, executes data requests, and renders 6 executive KPI cards with live values.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified submitting order date '2026-07-17' reloads KPI cards, bar chart, scatter plot, and data table with date records.</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified bar chart returns data array containing warehouse labels and cases built values for active facilities.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified scatter plot returns data array containing numeric order quantity and cases built coordinate points.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified analytics column service categorizes columns into numeric and categorical feature lists.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Random Forest model training fits features and returns accuracy evaluation metrics.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Logistic Regression training fits features and returns accuracy performance metrics.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified training both classifiers executes successfully and returns comparative performance metrics.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified requesting invalid target column returns clear validation error message.</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified querying model results before training indicates no models have been trained yet.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified bar chart calculation engine returns aggregated cases built totals for each active warehouse facility.</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting custom metric calculates average metric values for each warehouse facility.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified invalid column parameter gracefully falls back to default warehouse aggregation without failure.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified scatter plot extracts valid numeric coordinate pairs for visualization.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified heatmap service calculates correlation matrix containing x, y, and correlation scores.</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified distribution service calculates histogram bins with range labels and row counts.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified charts service reads SQL summary totals and returns aligned Cases Built numbers for facilities.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified warehouse statistics service retrieves line items array, total count, and pagination details.</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified querying warehouse statistics without date filter returns full dataset items across all dates.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified navigation bar renders AgenticOps AI branding logo and top-level navigation links.</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sales analytics component renders table headers, pagination controls, and filter inputs.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified inventory risk component exports functional component with risk forecasting logic.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified warehouse service connects to PostgreSQL database and returns inventory line items and totals.</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified data table component processes external filter properties and dynamically sets warehouse and scratch filters.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sample data service returns structured payload containing 100 row objects.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified requesting 50 sample rows returns payload containing exactly 50 row objects.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified dataset summary service calculates summary details containing row count and column statistics.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified uploading non-CSV file reports validation error rejecting invalid file type.</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified uploading valid CSV file parses rows, updates active dataset, and confirms record count.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified order date is formatted to YYYYMMDD and filtered in query returning matching order date rows.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified returned line items contain required keys: whs_num, batch_id, oerdte, cases_bld_stg, orgnl_ordr_qty_stg, and whs_scrtch_qty_stg.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified checking 'Filter Scratches' reloads data table displaying exclusively line items with scratch quantity &gt; 0.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting 'Whse 58' from dropdown reloads table displaying exclusively rows matching Warehouse 58.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking pagination button fetches page 2, updating row count indicator to loaded items.</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified anomaly scanner retrieves risk alert objects containing severity, title, message, and warehouse location.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified anomaly scanner outputs risk alerts with severity ratings (Critical, Warning, Info) and facility locations.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Anomaly Alert Panel renders risk cards with colored severity badges (Critical Red, Warning Amber, Info Cyan).</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking 'Filter Table' on anomaly card updates table filters and displays matching Warehouse line items.</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified workspace listing retrieves workspace array containing agentbuilder and project IDs.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting All Projects aggregates tasks from AgenticOps AI, AAD, and agentbuilder projects.</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified task objects contain exact project_name tags ('AgenticOps AI - Enterprise Control Plane', 'AI Analytics Dashboard').</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified SprintBoard.jsx renders 4 distinct Kanban columns for Backlog, To Do, In Progress, and Completed.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified changing workspace or project scope reloads sprint board tasks and updates project badges.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AgentMonitor.jsx and AgentTaskActivityTracker.jsx render running status table and live execution stream.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Playwright browser inspects select elements and confirms dark background colors (rgb(30, 41, 59)) with crisp option styling.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified server_health.servers_healthy() reports accurate up/down status for both application ports.</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified ensure_servers_running() starts missing services and browser tests proceed without connection refused errors.</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified agent_watchdog.py restarts offline services without manual user intervention.</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sprint_watcher_agent calls ensure_servers_running() before invoking tester_agent for unit and browser tests.</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3208,36 +3208,36 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AGENT_PICKUP_GROUPS excludes backlog and unit test test_pickup_groups_excludes_backlog passes.</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  📋 Sprint Task: Data Analytics</t>
+          <t xml:space="preserve">  📋 Sprint Task: Add Aditional Features</t>
         </is>
       </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Data Analytics</t>
+          <t>📋 Sprint Task: Add Aditional Features</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-1150CF09-SMOKE</t>
+          <t>TC-TASK-B1CE165D-SMOKE</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Dashboard smoke after sprint task: Data Analytics</t>
+          <t>Dashboard smoke after sprint task: Add Aditional Features</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>After implementing the sprint task 'Data Analytics', the main dashboard loads with KPI cards and global header controls working.</t>
+          <t>After implementing the sprint task 'Add Aditional Features', the main dashboard loads with KPI cards and global header controls working.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -3255,7 +3255,7 @@
           <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G81" s="10" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3264,27 +3264,27 @@
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Data Analytics</t>
+          <t>📋 Sprint Task: Add Aditional Features</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-1150CF09-COPILOT</t>
+          <t>TC-TASK-B1CE165D-AGENTS</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>AI Data Copilot accepts prompts and shows results</t>
+          <t>Agent status telemetry visible in sidebar</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>AI Data Copilot Sprint Task Verification</t>
+          <t>Agent Fleet Monitoring Verification</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
+          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
@@ -3292,7 +3292,7 @@
           <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="G82" s="10" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3301,27 +3301,27 @@
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Data Analytics</t>
+          <t>📋 Sprint Task: Add Aditional Features</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-1150CF09-TABLE</t>
+          <t>TC-TASK-B1CE165D-UPTIME</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Warehouse sales table loads with data rows</t>
+          <t>Application servers respond for browser testing</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Warehouse Analytics Table Verification</t>
+          <t>Application Uptime Verification</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -3329,587 +3329,472 @@
           <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="G83" s="10" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>📋 Sprint Task: Data Analytics</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>TC-TASK-1150CF09-HEADER</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>Global header controls and clear filter work</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>Header Controls Sprint Task Verification</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>Awaiting browser test execution for this sprint task case.</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Data Analytics</t>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-1150CF09-AGENTS</t>
+          <t>TC-COMP-01</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Agent status telemetry visible in sidebar</t>
+          <t>Dashboard Date+DB Submit KPI Alignment</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Agent Fleet Monitoring Verification</t>
+          <t>Comprehensive Dashboard Filter Engine</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Awaiting browser test execution for this sprint task case.</t>
+          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Data Analytics</t>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-1150CF09-UPTIME</t>
+          <t>TC-COMP-02</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Application servers respond for browser testing</t>
+          <t>Warehouse Filter Bar Chart Calculation</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Application Uptime Verification</t>
+          <t>Warehouse Bar Chart Calculation Verifier</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
+          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Awaiting browser test execution for this sprint task case.</t>
+          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-03</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Table Summary Cards API Alignment</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Warehouse Table Summary Calculation Engine</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="88" ht="36" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-01</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>Dashboard Date+DB Submit KPI Alignment</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>Comprehensive Dashboard Filter Engine</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
-        </is>
-      </c>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-04</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Search Without Date Parameter</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Date-Agnostic Search Engine</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="89" ht="36" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-02</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>Warehouse Filter Bar Chart Calculation</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>Warehouse Bar Chart Calculation Verifier</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-05</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Analytics Screen ML Controls</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Analytics Module Browser Smoke Test</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified Analytics page loads with model training controls visible.</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="90" ht="36" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-03</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Table Summary Cards API Alignment</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Warehouse Table Summary Calculation Engine</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-06</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Board All Dropdowns + Columns</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Board Comprehensive Module Test</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="91" ht="36" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-04</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Search Without Date Parameter</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Date-Agnostic Search Engine</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
-        </is>
-      </c>
-      <c r="G91" s="10" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-07</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Agent Monitor Fleet Screen</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Agent Monitor Module Browser Test</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="92" ht="36" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-05</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>Analytics Screen ML Controls</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>Analytics Module Browser Smoke Test</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified Analytics page loads with model training controls visible.</t>
-        </is>
-      </c>
-      <c r="G92" s="10" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-08</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Screen Load</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Module Browser Test</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="93" ht="36" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-06</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>Sprint Board All Dropdowns + Columns</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>Sprint Board Comprehensive Module Test</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
-        </is>
-      </c>
-      <c r="G93" s="10" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-09</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Full Filter Chain Scratch Submit</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Scratch Filter Propagation Engine</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="94" ht="36" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-07</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Agent Monitor Fleet Screen</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>Agent Monitor Module Browser Test</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
-        </is>
-      </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-10</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>Single Warehouse KPI vs Bar Chart Parity</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>Cross-Widget Calculation Parity Engine</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="95" ht="36" customHeight="1">
-      <c r="A95" s="7" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-08</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>MCP Explorer Screen Load</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>MCP Explorer Module Browser Test</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
-        </is>
-      </c>
-      <c r="G95" s="10" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-11</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Global Submit Uses Date Parameter</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Global Header Filter Engine</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="96" ht="36" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-09</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Full Filter Chain Scratch Submit</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>Scratch Filter Propagation Engine</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
-        </is>
-      </c>
-      <c r="G96" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="36" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-10</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>Single Warehouse KPI vs Bar Chart Parity</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>Cross-Widget Calculation Parity Engine</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
-        </is>
-      </c>
-      <c r="G97" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="36" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-11</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>Global Submit Uses Date Parameter</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>Global Header Filter Engine</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
-        </is>
-      </c>
-      <c r="G98" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="36" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>TC-COMP-12</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C96" s="9" t="inlineStr">
         <is>
           <t>Copilot Two Warehouses Different KPI</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
+      <c r="D96" s="9" t="inlineStr">
         <is>
           <t>Copilot Warehouse Calculation Engine</t>
         </is>
       </c>
-      <c r="E99" s="9" t="inlineStr">
+      <c r="E96" s="9" t="inlineStr">
         <is>
           <t>Discover two warehouses from API; Copilot queries must return different Cases Built totals per facility.</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>tests\browser\test_comprehensive_module_suite.py:353: in test_copilot_two_warehouses_different_kpi
-    assert_cases_aligned(cases_a, exp_a)
-tests\browser\calculation_verifier.py:114: in assert_cases_aligned
-    assert diff &lt;= allowed, (
-E   AssertionError: Cases built mismatch: API=0 UI=8,500 (diff=8,500)</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified Copilot warehouse filter returns distinct per-facility calculations from live API.</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="A61:G61"/>
     <mergeCell ref="A74:G74"/>
     <mergeCell ref="A80:G80"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A87:G87"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A10:G10"/>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -51,13 +51,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00166534"/>
+      <color rgb="00991B1B"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00166534"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -82,8 +82,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,8 +94,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -606,12 +606,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified agent status telemetry reports all 6 agent fleet processes active in RUNNING state.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -643,12 +643,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified system health check confirms healthy operational status and active database pool.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified data router operational status and confirmed data service readiness.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified system metadata confirming platform title AgenticOps AI and version 1.0.0.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified parameter-driven query routing executes seamlessly against requested target database.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified DEV database connection retrieves active warehouse inventory records.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified switching database reloads KPI cards, bar charts, and data tables with matching database metrics.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified AI Copilot historical date query bypasses date constraints and retrieves complete warehouse statistics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified AI Copilot search without date filter returns summary finding statements and metric totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified server-side date override executes full-dataset analysis across all historical dates.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot generates clear summary answer detailing invoice counts, cases built, and scratch quantities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified prompt '58 warehouse overview' extracts Warehouse 58 and filters chart data strictly to facility 58.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified query 'high scratch quantity' detects scratch intent and returns scratch item totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot search payload contains summary answers, applied filters, metrics, and chart data.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified submitting Copilot prompt renders summary card with matching metric counts.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot prompt updates Copilot chart, KPI cards, main bar chart, scatter plot, anomaly panel, and table.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified clicking clear button resets Copilot mode, hides banner, and restores baseline dashboard widgets.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified asking 'high scratch quantity' sets scratch filter and reloads table showing scratch rows.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified summary metrics return card data matching Cases Built, Order Qty, Invoices, and Active Warehouses.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified KPI metrics engine accepts all filter parameters and returns updated totals specific to criteria.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified dashboard loads cleanly, executes data requests, and renders 6 executive KPI cards with live values.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified submitting order date '2026-07-17' reloads KPI cards, bar chart, scatter plot, and data table with date records.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart returns data array containing warehouse labels and cases built values for active facilities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified scatter plot returns data array containing numeric order quantity and cases built coordinate points.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified analytics column service categorizes columns into numeric and categorical feature lists.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Random Forest model training fits features and returns accuracy evaluation metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Logistic Regression training fits features and returns accuracy performance metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified training both classifiers executes successfully and returns comparative performance metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified requesting invalid target column returns clear validation error message.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified querying model results before training indicates no models have been trained yet.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart calculation engine returns aggregated cases built totals for each active warehouse facility.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting custom metric calculates average metric values for each warehouse facility.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified invalid column parameter gracefully falls back to default warehouse aggregation without failure.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified scatter plot extracts valid numeric coordinate pairs for visualization.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified heatmap service calculates correlation matrix containing x, y, and correlation scores.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified distribution service calculates histogram bins with range labels and row counts.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified charts service reads SQL summary totals and returns aligned Cases Built numbers for facilities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified warehouse statistics service retrieves line items array, total count, and pagination details.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified querying warehouse statistics without date filter returns full dataset items across all dates.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified navigation bar renders AgenticOps AI branding logo and top-level navigation links.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sales analytics component renders table headers, pagination controls, and filter inputs.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified inventory risk component exports functional component with risk forecasting logic.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified warehouse service connects to PostgreSQL database and returns inventory line items and totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified data table component processes external filter properties and dynamically sets warehouse and scratch filters.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sample data service returns structured payload containing 100 row objects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified requesting 50 sample rows returns payload containing exactly 50 row objects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified dataset summary service calculates summary details containing row count and column statistics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified uploading non-CSV file reports validation error rejecting invalid file type.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified uploading valid CSV file parses rows, updates active dataset, and confirms record count.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified order date is formatted to YYYYMMDD and filtered in query returning matching order date rows.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified returned line items contain required keys: whs_num, batch_id, oerdte, cases_bld_stg, orgnl_ordr_qty_stg, and whs_scrtch_qty_stg.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified checking 'Filter Scratches' reloads data table displaying exclusively line items with scratch quantity &gt; 0.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting 'Whse 58' from dropdown reloads table displaying exclusively rows matching Warehouse 58.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified clicking pagination button fetches page 2, updating row count indicator to loaded items.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified anomaly scanner retrieves risk alert objects containing severity, title, message, and warehouse location.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified anomaly scanner outputs risk alerts with severity ratings (Critical, Warning, Info) and facility locations.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Anomaly Alert Panel renders risk cards with colored severity badges (Critical Red, Warning Amber, Info Cyan).</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified clicking 'Filter Table' on anomaly card updates table filters and displays matching Warehouse line items.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified workspace listing retrieves workspace array containing agentbuilder and project IDs.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting All Projects aggregates tasks from AgenticOps AI, AAD, and agentbuilder projects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified task objects contain exact project_name tags ('AgenticOps AI - Enterprise Control Plane', 'AI Analytics Dashboard').</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified SprintBoard.jsx renders 4 distinct Kanban columns for Backlog, To Do, In Progress, and Completed.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified changing workspace or project scope reloads sprint board tasks and updates project badges.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified AgentMonitor.jsx and AgentTaskActivityTracker.jsx render running status table and live execution stream.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Playwright browser inspects select elements and confirms dark background colors (rgb(30, 41, 59)) with crisp option styling.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified server_health.servers_healthy() reports accurate up/down status for both application ports.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified ensure_servers_running() starts missing services and browser tests proceed without connection refused errors.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified agent_watchdog.py restarts offline services without manual user intervention.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sprint_watcher_agent calls ensure_servers_running() before invoking tester_agent for unit and browser tests.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified AGENT_PICKUP_GROUPS excludes backlog and unit test test_pickup_groups_excludes_backlog passes.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
           <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3292,7 +3292,7 @@
           <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3329,7 +3329,7 @@
           <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3373,7 +3373,7 @@
           <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G85" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3410,7 +3410,7 @@
           <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="G86" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3447,7 +3447,7 @@
           <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G87" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3484,7 +3484,7 @@
           <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G88" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3521,7 +3521,7 @@
           <t>Successfully verified Analytics page loads with model training controls visible.</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3558,7 +3558,7 @@
           <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="G90" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3595,7 +3595,7 @@
           <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="G91" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3632,7 +3632,7 @@
           <t>Successfully verified MCP Explorer page loads with server registry content.</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3669,7 +3669,7 @@
           <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G93" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3706,7 +3706,7 @@
           <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3743,7 +3743,7 @@
           <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3777,12 +3777,16 @@
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot warehouse filter returns distinct per-facility calculations from live API.</t>
+          <t>tests\browser\test_comprehensive_module_suite.py:353: in test_copilot_two_warehouses_different_kpi
+    assert_cases_aligned(cases_a, exp_a)
+tests\browser\calculation_verifier.py:114: in assert_cases_aligned
+    assert diff &lt;= allowed, (
+E   AssertionError: Cases built mismatch: API=0 UI=8,500 (diff=8,500)</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -3777,16 +3777,12 @@
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>tests\browser\test_comprehensive_module_suite.py:353: in test_copilot_two_warehouses_different_kpi
-    assert_cases_aligned(cases_a, exp_a)
-tests\browser\calculation_verifier.py:114: in assert_cases_aligned
-    assert diff &lt;= allowed, (
-E   AssertionError: Cases built mismatch: API=0 UI=8,500 (diff=8,500)</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Successfully verified Copilot warehouse filter returns distinct per-facility calculations from live API.</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,17 +51,11 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="00166534"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,20 +76,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
         <bgColor rgb="00F8FAFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -153,9 +141,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -606,12 +591,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified agent status telemetry reports all 6 agent fleet processes active in RUNNING state.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -643,12 +628,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified system health check confirms healthy operational status and active database pool.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -680,12 +665,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified data router operational status and confirmed data service readiness.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -717,12 +702,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified system metadata confirming platform title AgenticOps AI and version 1.0.0.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -754,12 +739,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified parameter-driven query routing executes seamlessly against requested target database.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -791,12 +776,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified DEV database connection retrieves active warehouse inventory records.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -828,12 +813,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified switching database reloads KPI cards, bar charts, and data tables with matching database metrics.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -872,12 +857,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AI Copilot historical date query bypasses date constraints and retrieves complete warehouse statistics.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -909,12 +894,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AI Copilot search without date filter returns summary finding statements and metric totals.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -946,12 +931,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified server-side date override executes full-dataset analysis across all historical dates.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -983,12 +968,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot generates clear summary answer detailing invoice counts, cases built, and scratch quantities.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1005,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified prompt '58 warehouse overview' extracts Warehouse 58 and filters chart data strictly to facility 58.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1042,12 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified query 'high scratch quantity' detects scratch intent and returns scratch item totals.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1079,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot search payload contains summary answers, applied filters, metrics, and chart data.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1116,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified submitting Copilot prompt renders summary card with matching metric counts.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1153,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot prompt updates Copilot chart, KPI cards, main bar chart, scatter plot, anomaly panel, and table.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1190,12 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking clear button resets Copilot mode, hides banner, and restores baseline dashboard widgets.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1227,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified asking 'high scratch quantity' sets scratch filter and reloads table showing scratch rows.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1271,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified summary metrics return card data matching Cases Built, Order Qty, Invoices, and Active Warehouses.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1308,12 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified KPI metrics engine accepts all filter parameters and returns updated totals specific to criteria.</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1345,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified dashboard loads cleanly, executes data requests, and renders 6 executive KPI cards with live values.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1382,12 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified submitting order date '2026-07-17' reloads KPI cards, bar chart, scatter plot, and data table with date records.</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1426,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified bar chart returns data array containing warehouse labels and cases built values for active facilities.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1463,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified scatter plot returns data array containing numeric order quantity and cases built coordinate points.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1500,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified analytics column service categorizes columns into numeric and categorical feature lists.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1537,12 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Random Forest model training fits features and returns accuracy evaluation metrics.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1574,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Logistic Regression training fits features and returns accuracy performance metrics.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1611,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified training both classifiers executes successfully and returns comparative performance metrics.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1648,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified requesting invalid target column returns clear validation error message.</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1685,12 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified querying model results before training indicates no models have been trained yet.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1722,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified bar chart calculation engine returns aggregated cases built totals for each active warehouse facility.</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1759,12 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting custom metric calculates average metric values for each warehouse facility.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1796,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified invalid column parameter gracefully falls back to default warehouse aggregation without failure.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1833,12 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified scatter plot extracts valid numeric coordinate pairs for visualization.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1870,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified heatmap service calculates correlation matrix containing x, y, and correlation scores.</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1907,12 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified distribution service calculates histogram bins with range labels and row counts.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1944,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified charts service reads SQL summary totals and returns aligned Cases Built numbers for facilities.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2003,12 +1988,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified warehouse statistics service retrieves line items array, total count, and pagination details.</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2025,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified querying warehouse statistics without date filter returns full dataset items across all dates.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2062,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified navigation bar renders AgenticOps AI branding logo and top-level navigation links.</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2099,12 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sales analytics component renders table headers, pagination controls, and filter inputs.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2136,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified inventory risk component exports functional component with risk forecasting logic.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2173,12 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified warehouse service connects to PostgreSQL database and returns inventory line items and totals.</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2210,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified data table component processes external filter properties and dynamically sets warehouse and scratch filters.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2247,12 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sample data service returns structured payload containing 100 row objects.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2284,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified requesting 50 sample rows returns payload containing exactly 50 row objects.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2321,12 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified dataset summary service calculates summary details containing row count and column statistics.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2358,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified uploading non-CSV file reports validation error rejecting invalid file type.</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2395,12 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified uploading valid CSV file parses rows, updates active dataset, and confirms record count.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2432,12 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified order date is formatted to YYYYMMDD and filtered in query returning matching order date rows.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2469,12 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified returned line items contain required keys: whs_num, batch_id, oerdte, cases_bld_stg, orgnl_ordr_qty_stg, and whs_scrtch_qty_stg.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2506,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified checking 'Filter Scratches' reloads data table displaying exclusively line items with scratch quantity &gt; 0.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2543,12 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting 'Whse 58' from dropdown reloads table displaying exclusively rows matching Warehouse 58.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2580,12 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking pagination button fetches page 2, updating row count indicator to loaded items.</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2624,12 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified anomaly scanner retrieves risk alert objects containing severity, title, message, and warehouse location.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2661,12 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified anomaly scanner outputs risk alerts with severity ratings (Critical, Warning, Info) and facility locations.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2698,12 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Anomaly Alert Panel renders risk cards with colored severity badges (Critical Red, Warning Amber, Info Cyan).</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2735,12 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking 'Filter Table' on anomaly card updates table filters and displays matching Warehouse line items.</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2779,12 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified workspace listing retrieves workspace array containing agentbuilder and project IDs.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2816,12 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting All Projects aggregates tasks from AgenticOps AI, AAD, and agentbuilder projects.</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2868,12 +2853,12 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified task objects contain exact project_name tags ('AgenticOps AI - Enterprise Control Plane', 'AI Analytics Dashboard').</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2890,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified SprintBoard.jsx renders 4 distinct Kanban columns for Backlog, To Do, In Progress, and Completed.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2927,12 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified changing workspace or project scope reloads sprint board tasks and updates project badges.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2964,12 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AgentMonitor.jsx and AgentTaskActivityTracker.jsx render running status table and live execution stream.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3001,12 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Playwright browser inspects select elements and confirms dark background colors (rgb(30, 41, 59)) with crisp option styling.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3045,12 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified server_health.servers_healthy() reports accurate up/down status for both application ports.</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3082,12 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified ensure_servers_running() starts missing services and browser tests proceed without connection refused errors.</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3119,12 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified agent_watchdog.py restarts offline services without manual user intervention.</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3156,12 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sprint_watcher_agent calls ensure_servers_running() before invoking tester_agent for unit and browser tests.</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3208,36 +3193,36 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AGENT_PICKUP_GROUPS excludes backlog and unit test test_pickup_groups_excludes_backlog passes.</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  📋 Sprint Task: Add Aditional Features</t>
+          <t xml:space="preserve">  📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Add Aditional Features</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-B1CE165D-SMOKE</t>
+          <t>TC-TASK-TEST-TAS-SMOKE</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Dashboard smoke after sprint task: Add Aditional Features</t>
+          <t>Dashboard smoke after sprint task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3247,133 +3232,163 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>After implementing the sprint task 'Add Aditional Features', the main dashboard loads with KPI cards and global header controls working.</t>
+          <t>After implementing the sprint task 'Sprint Board Browser Navigation', the main dashboard loads with KPI cards and global header controls working.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Awaiting browser test execution for this sprint task case.</t>
+          <t>Successfully verified in browser: After implementing the sprint task 'Sprint Board Browser Navigation', the main dashboard loads with KPI cards and global</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Add Aditional Features</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-B1CE165D-AGENTS</t>
+          <t>TC-TASK-TEST-TAS-SPRINT-UI</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Agent status telemetry visible in sidebar</t>
+          <t>Sprint board page loads with workspace and project selectors</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Agent Fleet Monitoring Verification</t>
+          <t>Sprint Board Browser Verification</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+          <t>The Sprint Board page displays workspace and project dropdowns and kanban column headers.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Awaiting browser test execution for this sprint task case.</t>
+          <t>Successfully verified in browser: The Sprint Board page displays workspace and project dropdowns and kanban column headers.</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Add Aditional Features</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-B1CE165D-UPTIME</t>
+          <t>TC-TASK-TEST-TAS-COPILOT</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Application servers respond for browser testing</t>
+          <t>AI Data Copilot accepts prompts and shows results</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Application Uptime Verification</t>
+          <t>AI Data Copilot Sprint Task Verification</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
+          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Awaiting browser test execution for this sprint task case.</t>
+          <t>Successfully verified in browser: The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>TC-TASK-TEST-TAS-TABLE</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse sales table loads with data rows</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse Analytics Table Verification</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified in browser: Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-01</t>
+          <t>TC-TASK-TEST-TAS-HEADER</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Dashboard Date+DB Submit KPI Alignment</t>
+          <t>Global header controls and clear filter work</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Comprehensive Dashboard Filter Engine</t>
+          <t>Header Controls Sprint Task Verification</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
+          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
+          <t>Successfully verified in browser: Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3382,35 +3397,35 @@
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-02</t>
+          <t>TC-TASK-TEST-TAS-AGENTS</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Warehouse Filter Bar Chart Calculation</t>
+          <t>Agent status telemetry visible in sidebar</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Warehouse Bar Chart Calculation Verifier</t>
+          <t>Agent Fleet Monitoring Verification</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
+          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr">
+          <t>Successfully verified in browser: The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3419,74 +3434,44 @@
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-03</t>
+          <t>TC-TASK-TEST-TAS-UPTIME</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Table Summary Cards API Alignment</t>
+          <t>Application servers respond for browser testing</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Warehouse Table Summary Calculation Engine</t>
+          <t>Application Uptime Verification</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
+          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
-        </is>
-      </c>
-      <c r="G87" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="36" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-04</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Search Without Date Parameter</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Date-Agnostic Search Engine</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
-        </is>
-      </c>
-      <c r="G88" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Successfully verified in browser: The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
     </row>
@@ -3498,30 +3483,30 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-05</t>
+          <t>TC-COMP-01</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Analytics Screen ML Controls</t>
+          <t>Dashboard Date+DB Submit KPI Alignment</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Analytics Module Browser Smoke Test</t>
+          <t>Comprehensive Dashboard Filter Engine</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
+          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Analytics page loads with model training controls visible.</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
+          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3535,30 +3520,30 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-06</t>
+          <t>TC-COMP-02</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Sprint Board All Dropdowns + Columns</t>
+          <t>Warehouse Filter Bar Chart Calculation</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Sprint Board Comprehensive Module Test</t>
+          <t>Warehouse Bar Chart Calculation Verifier</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
+          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
+          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3572,30 +3557,30 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-07</t>
+          <t>TC-COMP-03</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Agent Monitor Fleet Screen</t>
+          <t>Table Summary Cards API Alignment</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Agent Monitor Module Browser Test</t>
+          <t>Warehouse Table Summary Calculation Engine</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
+          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
-        </is>
-      </c>
-      <c r="G91" s="10" t="inlineStr">
+          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3609,30 +3594,30 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-08</t>
+          <t>TC-COMP-04</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>MCP Explorer Screen Load</t>
+          <t>Copilot Search Without Date Parameter</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>MCP Explorer Module Browser Test</t>
+          <t>Copilot Date-Agnostic Search Engine</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
+          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
-        </is>
-      </c>
-      <c r="G92" s="10" t="inlineStr">
+          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3646,30 +3631,30 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-09</t>
+          <t>TC-COMP-05</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Full Filter Chain Scratch Submit</t>
+          <t>Analytics Screen ML Controls</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Scratch Filter Propagation Engine</t>
+          <t>Analytics Module Browser Smoke Test</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
+          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
-        </is>
-      </c>
-      <c r="G93" s="10" t="inlineStr">
+          <t>Successfully verified Analytics page loads with model training controls visible.</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3683,30 +3668,30 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-10</t>
+          <t>TC-COMP-06</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Single Warehouse KPI vs Bar Chart Parity</t>
+          <t>Sprint Board All Dropdowns + Columns</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Cross-Widget Calculation Parity Engine</t>
+          <t>Sprint Board Comprehensive Module Test</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
+          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
-        </is>
-      </c>
-      <c r="G94" s="10" t="inlineStr">
+          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3720,30 +3705,30 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-11</t>
+          <t>TC-COMP-07</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Global Submit Uses Date Parameter</t>
+          <t>Agent Monitor Fleet Screen</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Global Header Filter Engine</t>
+          <t>Agent Monitor Module Browser Test</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
+          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
-        </is>
-      </c>
-      <c r="G95" s="10" t="inlineStr">
+          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3757,30 +3742,178 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
+          <t>TC-COMP-08</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Screen Load</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Module Browser Test</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-09</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Full Filter Chain Scratch Submit</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Scratch Filter Propagation Engine</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-10</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Single Warehouse KPI vs Bar Chart Parity</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>Cross-Widget Calculation Parity Engine</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-11</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Global Submit Uses Date Parameter</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Global Header Filter Engine</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
           <t>TC-COMP-12</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C100" s="9" t="inlineStr">
         <is>
           <t>Copilot Two Warehouses Different KPI</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="D100" s="9" t="inlineStr">
         <is>
           <t>Copilot Warehouse Calculation Engine</t>
         </is>
       </c>
-      <c r="E96" s="9" t="inlineStr">
+      <c r="E100" s="9" t="inlineStr">
         <is>
           <t>Discover two warehouses from API; Copilot queries must return different Cases Built totals per facility.</t>
         </is>
       </c>
-      <c r="F96" s="9" t="inlineStr">
+      <c r="F100" s="9" t="inlineStr">
         <is>
           <t>Successfully verified Copilot warehouse filter returns distinct per-facility calculations from live API.</t>
         </is>
       </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3788,11 +3921,11 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="A61:G61"/>
     <mergeCell ref="A74:G74"/>
     <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A88:G88"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A2:G2"/>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,11 +51,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00166534"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,14 +82,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
         <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +153,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -591,12 +606,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified agent status telemetry reports all 6 agent fleet processes active in RUNNING state.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -628,12 +643,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified system health check confirms healthy operational status and active database pool.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -665,12 +680,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified data router operational status and confirmed data service readiness.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -702,12 +717,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified system metadata confirming platform title AgenticOps AI and version 1.0.0.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -739,12 +754,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified parameter-driven query routing executes seamlessly against requested target database.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -776,12 +791,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified DEV database connection retrieves active warehouse inventory records.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -813,12 +828,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified switching database reloads KPI cards, bar charts, and data tables with matching database metrics.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -857,12 +872,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified AI Copilot historical date query bypasses date constraints and retrieves complete warehouse statistics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -894,12 +909,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified AI Copilot search without date filter returns summary finding statements and metric totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -931,12 +946,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified server-side date override executes full-dataset analysis across all historical dates.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -968,12 +983,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot generates clear summary answer detailing invoice counts, cases built, and scratch quantities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1020,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified prompt '58 warehouse overview' extracts Warehouse 58 and filters chart data strictly to facility 58.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1057,12 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified query 'high scratch quantity' detects scratch intent and returns scratch item totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1094,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot search payload contains summary answers, applied filters, metrics, and chart data.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1131,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified submitting Copilot prompt renders summary card with matching metric counts.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1168,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot prompt updates Copilot chart, KPI cards, main bar chart, scatter plot, anomaly panel, and table.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1205,12 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified clicking clear button resets Copilot mode, hides banner, and restores baseline dashboard widgets.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1242,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified asking 'high scratch quantity' sets scratch filter and reloads table showing scratch rows.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1286,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified summary metrics return card data matching Cases Built, Order Qty, Invoices, and Active Warehouses.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1323,12 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified KPI metrics engine accepts all filter parameters and returns updated totals specific to criteria.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1360,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified dashboard loads cleanly, executes data requests, and renders 6 executive KPI cards with live values.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1397,12 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified submitting order date '2026-07-17' reloads KPI cards, bar chart, scatter plot, and data table with date records.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1441,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart returns data array containing warehouse labels and cases built values for active facilities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1478,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified scatter plot returns data array containing numeric order quantity and cases built coordinate points.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1515,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified analytics column service categorizes columns into numeric and categorical feature lists.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1552,12 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Random Forest model training fits features and returns accuracy evaluation metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1589,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Logistic Regression training fits features and returns accuracy performance metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1626,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified training both classifiers executes successfully and returns comparative performance metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1663,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified requesting invalid target column returns clear validation error message.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1700,12 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified querying model results before training indicates no models have been trained yet.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1737,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart calculation engine returns aggregated cases built totals for each active warehouse facility.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1774,12 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting custom metric calculates average metric values for each warehouse facility.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1811,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified invalid column parameter gracefully falls back to default warehouse aggregation without failure.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1848,12 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified scatter plot extracts valid numeric coordinate pairs for visualization.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1885,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified heatmap service calculates correlation matrix containing x, y, and correlation scores.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1922,12 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified distribution service calculates histogram bins with range labels and row counts.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1959,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified charts service reads SQL summary totals and returns aligned Cases Built numbers for facilities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1988,12 +2003,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified warehouse statistics service retrieves line items array, total count, and pagination details.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2040,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified querying warehouse statistics without date filter returns full dataset items across all dates.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2077,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified navigation bar renders AgenticOps AI branding logo and top-level navigation links.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2114,12 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sales analytics component renders table headers, pagination controls, and filter inputs.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2151,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified inventory risk component exports functional component with risk forecasting logic.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2188,12 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified warehouse service connects to PostgreSQL database and returns inventory line items and totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2225,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified data table component processes external filter properties and dynamically sets warehouse and scratch filters.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2247,12 +2262,12 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sample data service returns structured payload containing 100 row objects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2299,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified requesting 50 sample rows returns payload containing exactly 50 row objects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2336,12 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified dataset summary service calculates summary details containing row count and column statistics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2373,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified uploading non-CSV file reports validation error rejecting invalid file type.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2395,12 +2410,12 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified uploading valid CSV file parses rows, updates active dataset, and confirms record count.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2447,12 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified order date is formatted to YYYYMMDD and filtered in query returning matching order date rows.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2469,12 +2484,12 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified returned line items contain required keys: whs_num, batch_id, oerdte, cases_bld_stg, orgnl_ordr_qty_stg, and whs_scrtch_qty_stg.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2506,12 +2521,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified checking 'Filter Scratches' reloads data table displaying exclusively line items with scratch quantity &gt; 0.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2558,12 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting 'Whse 58' from dropdown reloads table displaying exclusively rows matching Warehouse 58.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2595,12 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified clicking pagination button fetches page 2, updating row count indicator to loaded items.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2639,12 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified anomaly scanner retrieves risk alert objects containing severity, title, message, and warehouse location.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2676,12 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified anomaly scanner outputs risk alerts with severity ratings (Critical, Warning, Info) and facility locations.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2713,12 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Anomaly Alert Panel renders risk cards with colored severity badges (Critical Red, Warning Amber, Info Cyan).</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2750,12 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified clicking 'Filter Table' on anomaly card updates table filters and displays matching Warehouse line items.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2794,12 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified workspace listing retrieves workspace array containing agentbuilder and project IDs.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2831,12 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting All Projects aggregates tasks from AgenticOps AI, AAD, and agentbuilder projects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2868,12 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified task objects contain exact project_name tags ('AgenticOps AI - Enterprise Control Plane', 'AI Analytics Dashboard').</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2905,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified SprintBoard.jsx renders 4 distinct Kanban columns for Backlog, To Do, In Progress, and Completed.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2927,12 +2942,12 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified changing workspace or project scope reloads sprint board tasks and updates project badges.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2964,12 +2979,12 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified AgentMonitor.jsx and AgentTaskActivityTracker.jsx render running status table and live execution stream.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3016,12 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Playwright browser inspects select elements and confirms dark background colors (rgb(30, 41, 59)) with crisp option styling.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3045,12 +3060,12 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified server_health.servers_healthy() reports accurate up/down status for both application ports.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3097,12 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified ensure_servers_running() starts missing services and browser tests proceed without connection refused errors.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3134,12 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified agent_watchdog.py restarts offline services without manual user intervention.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3171,12 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sprint_watcher_agent calls ensure_servers_running() before invoking tester_agent for unit and browser tests.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3208,12 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified AGENT_PICKUP_GROUPS excludes backlog and unit test test_pickup_groups_excludes_backlog passes.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3255,7 @@
           <t>Successfully verified in browser: After implementing the sprint task 'Sprint Board Browser Navigation', the main dashboard loads with KPI cards and global</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G81" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3277,7 +3292,7 @@
           <t>Successfully verified in browser: The Sprint Board page displays workspace and project dropdowns and kanban column headers.</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="G82" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3314,7 +3329,7 @@
           <t>Successfully verified in browser: The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="G83" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3351,7 +3366,7 @@
           <t>Successfully verified in browser: Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr">
+      <c r="G84" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3388,7 +3403,7 @@
           <t>Successfully verified in browser: Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G85" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3425,7 +3440,7 @@
           <t>Successfully verified in browser: The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="G86" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3462,7 +3477,7 @@
           <t>Successfully verified in browser: The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G87" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3506,7 +3521,7 @@
           <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3543,7 +3558,7 @@
           <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="G90" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3580,7 +3595,7 @@
           <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="G91" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3617,7 +3632,7 @@
           <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3654,7 +3669,7 @@
           <t>Successfully verified Analytics page loads with model training controls visible.</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G93" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3691,7 +3706,7 @@
           <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3728,7 +3743,7 @@
           <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3765,7 +3780,7 @@
           <t>Successfully verified MCP Explorer page loads with server registry content.</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3802,7 +3817,7 @@
           <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="G97" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3839,7 +3854,7 @@
           <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
         </is>
       </c>
-      <c r="G98" s="6" t="inlineStr">
+      <c r="G98" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3876,7 +3891,7 @@
           <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="G99" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3913,7 +3928,7 @@
           <t>Successfully verified Copilot warehouse filter returns distinct per-facility calculations from live API.</t>
         </is>
       </c>
-      <c r="G100" s="6" t="inlineStr">
+      <c r="G100" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -51,13 +51,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00166534"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00166534"/>
+      <color rgb="00991B1B"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -82,8 +82,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,8 +94,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -606,12 +606,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified agent status telemetry reports all 6 agent fleet processes active in RUNNING state.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -643,12 +643,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified system health check confirms healthy operational status and active database pool.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified data router operational status and confirmed data service readiness.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified system metadata confirming platform title AgenticOps AI and version 1.0.0.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified parameter-driven query routing executes seamlessly against requested target database.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified DEV database connection retrieves active warehouse inventory records.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified switching database reloads KPI cards, bar charts, and data tables with matching database metrics.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AI Copilot historical date query bypasses date constraints and retrieves complete warehouse statistics.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AI Copilot search without date filter returns summary finding statements and metric totals.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified server-side date override executes full-dataset analysis across all historical dates.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot generates clear summary answer detailing invoice counts, cases built, and scratch quantities.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified prompt '58 warehouse overview' extracts Warehouse 58 and filters chart data strictly to facility 58.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified query 'high scratch quantity' detects scratch intent and returns scratch item totals.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot search payload contains summary answers, applied filters, metrics, and chart data.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified submitting Copilot prompt renders summary card with matching metric counts.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot prompt updates Copilot chart, KPI cards, main bar chart, scatter plot, anomaly panel, and table.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking clear button resets Copilot mode, hides banner, and restores baseline dashboard widgets.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified asking 'high scratch quantity' sets scratch filter and reloads table showing scratch rows.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified summary metrics return card data matching Cases Built, Order Qty, Invoices, and Active Warehouses.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified KPI metrics engine accepts all filter parameters and returns updated totals specific to criteria.</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified dashboard loads cleanly, executes data requests, and renders 6 executive KPI cards with live values.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified submitting order date '2026-07-17' reloads KPI cards, bar chart, scatter plot, and data table with date records.</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified bar chart returns data array containing warehouse labels and cases built values for active facilities.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified scatter plot returns data array containing numeric order quantity and cases built coordinate points.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified analytics column service categorizes columns into numeric and categorical feature lists.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Random Forest model training fits features and returns accuracy evaluation metrics.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Logistic Regression training fits features and returns accuracy performance metrics.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified training both classifiers executes successfully and returns comparative performance metrics.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified requesting invalid target column returns clear validation error message.</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified querying model results before training indicates no models have been trained yet.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified bar chart calculation engine returns aggregated cases built totals for each active warehouse facility.</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting custom metric calculates average metric values for each warehouse facility.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified invalid column parameter gracefully falls back to default warehouse aggregation without failure.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified scatter plot extracts valid numeric coordinate pairs for visualization.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified heatmap service calculates correlation matrix containing x, y, and correlation scores.</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified distribution service calculates histogram bins with range labels and row counts.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified charts service reads SQL summary totals and returns aligned Cases Built numbers for facilities.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified warehouse statistics service retrieves line items array, total count, and pagination details.</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified querying warehouse statistics without date filter returns full dataset items across all dates.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified navigation bar renders AgenticOps AI branding logo and top-level navigation links.</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sales analytics component renders table headers, pagination controls, and filter inputs.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified inventory risk component exports functional component with risk forecasting logic.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified warehouse service connects to PostgreSQL database and returns inventory line items and totals.</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified data table component processes external filter properties and dynamically sets warehouse and scratch filters.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sample data service returns structured payload containing 100 row objects.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified requesting 50 sample rows returns payload containing exactly 50 row objects.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified dataset summary service calculates summary details containing row count and column statistics.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified uploading non-CSV file reports validation error rejecting invalid file type.</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified uploading valid CSV file parses rows, updates active dataset, and confirms record count.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified order date is formatted to YYYYMMDD and filtered in query returning matching order date rows.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified returned line items contain required keys: whs_num, batch_id, oerdte, cases_bld_stg, orgnl_ordr_qty_stg, and whs_scrtch_qty_stg.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified checking 'Filter Scratches' reloads data table displaying exclusively line items with scratch quantity &gt; 0.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting 'Whse 58' from dropdown reloads table displaying exclusively rows matching Warehouse 58.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking pagination button fetches page 2, updating row count indicator to loaded items.</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified anomaly scanner retrieves risk alert objects containing severity, title, message, and warehouse location.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified anomaly scanner outputs risk alerts with severity ratings (Critical, Warning, Info) and facility locations.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Anomaly Alert Panel renders risk cards with colored severity badges (Critical Red, Warning Amber, Info Cyan).</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking 'Filter Table' on anomaly card updates table filters and displays matching Warehouse line items.</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified workspace listing retrieves workspace array containing agentbuilder and project IDs.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting All Projects aggregates tasks from AgenticOps AI, AAD, and agentbuilder projects.</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified task objects contain exact project_name tags ('AgenticOps AI - Enterprise Control Plane', 'AI Analytics Dashboard').</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified SprintBoard.jsx renders 4 distinct Kanban columns for Backlog, To Do, In Progress, and Completed.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified changing workspace or project scope reloads sprint board tasks and updates project badges.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AgentMonitor.jsx and AgentTaskActivityTracker.jsx render running status table and live execution stream.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Playwright browser inspects select elements and confirms dark background colors (rgb(30, 41, 59)) with crisp option styling.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified server_health.servers_healthy() reports accurate up/down status for both application ports.</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified ensure_servers_running() starts missing services and browser tests proceed without connection refused errors.</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified agent_watchdog.py restarts offline services without manual user intervention.</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sprint_watcher_agent calls ensure_servers_running() before invoking tester_agent for unit and browser tests.</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3208,36 +3208,36 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AGENT_PICKUP_GROUPS excludes backlog and unit test test_pickup_groups_excludes_backlog passes.</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t xml:space="preserve">  📋 Sprint Task: Add Aditional Features</t>
         </is>
       </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>📋 Sprint Task: Add Aditional Features</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-SMOKE</t>
+          <t>TC-TASK-B1CE165D-SMOKE</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Dashboard smoke after sprint task: Sprint Board Browser Navigation</t>
+          <t>Dashboard smoke after sprint task: Add Aditional Features</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3247,163 +3247,133 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>After implementing the sprint task 'Sprint Board Browser Navigation', the main dashboard loads with KPI cards and global header controls working.</t>
+          <t>After implementing the sprint task 'Add Aditional Features', the main dashboard loads with KPI cards and global header controls working.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: After implementing the sprint task 'Sprint Board Browser Navigation', the main dashboard loads with KPI cards and global</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>📋 Sprint Task: Add Aditional Features</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-SPRINT-UI</t>
+          <t>TC-TASK-B1CE165D-AGENTS</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Sprint board page loads with workspace and project selectors</t>
+          <t>Agent status telemetry visible in sidebar</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Sprint Board Browser Verification</t>
+          <t>Agent Fleet Monitoring Verification</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>The Sprint Board page displays workspace and project dropdowns and kanban column headers.</t>
+          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: The Sprint Board page displays workspace and project dropdowns and kanban column headers.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>📋 Sprint Task: Add Aditional Features</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-COPILOT</t>
+          <t>TC-TASK-B1CE165D-UPTIME</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>AI Data Copilot accepts prompts and shows results</t>
+          <t>Application servers respond for browser testing</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>AI Data Copilot Sprint Task Verification</t>
+          <t>Application Uptime Verification</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
+          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>TC-TASK-TEST-TAS-TABLE</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>Warehouse sales table loads with data rows</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>Warehouse Analytics Table Verification</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified in browser: Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-HEADER</t>
+          <t>TC-COMP-01</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Global header controls and clear filter work</t>
+          <t>Dashboard Date+DB Submit KPI Alignment</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Header Controls Sprint Task Verification</t>
+          <t>Comprehensive Dashboard Filter Engine</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
+          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
+          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3412,35 +3382,35 @@
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-AGENTS</t>
+          <t>TC-COMP-02</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Agent status telemetry visible in sidebar</t>
+          <t>Warehouse Filter Bar Chart Calculation</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Agent Fleet Monitoring Verification</t>
+          <t>Warehouse Bar Chart Calculation Verifier</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr">
+          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3449,44 +3419,74 @@
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-UPTIME</t>
+          <t>TC-COMP-03</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Application servers respond for browser testing</t>
+          <t>Table Summary Cards API Alignment</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Application Uptime Verification</t>
+          <t>Warehouse Table Summary Calculation Engine</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
+          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
-        </is>
-      </c>
-      <c r="G87" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-04</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Search Without Date Parameter</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Date-Agnostic Search Engine</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3498,30 +3498,30 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-01</t>
+          <t>TC-COMP-05</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Dashboard Date+DB Submit KPI Alignment</t>
+          <t>Analytics Screen ML Controls</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Comprehensive Dashboard Filter Engine</t>
+          <t>Analytics Module Browser Smoke Test</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
+          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
+          <t>Successfully verified Analytics page loads with model training controls visible.</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3535,30 +3535,30 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-02</t>
+          <t>TC-COMP-06</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Warehouse Filter Bar Chart Calculation</t>
+          <t>Sprint Board All Dropdowns + Columns</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Warehouse Bar Chart Calculation Verifier</t>
+          <t>Sprint Board Comprehensive Module Test</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
+          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
+          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3572,30 +3572,30 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-03</t>
+          <t>TC-COMP-07</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Table Summary Cards API Alignment</t>
+          <t>Agent Monitor Fleet Screen</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Warehouse Table Summary Calculation Engine</t>
+          <t>Agent Monitor Module Browser Test</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
+          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
-        </is>
-      </c>
-      <c r="G91" s="10" t="inlineStr">
+          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3609,30 +3609,30 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-04</t>
+          <t>TC-COMP-08</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Copilot Search Without Date Parameter</t>
+          <t>MCP Explorer Screen Load</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Copilot Date-Agnostic Search Engine</t>
+          <t>MCP Explorer Module Browser Test</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
+          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
-        </is>
-      </c>
-      <c r="G92" s="10" t="inlineStr">
+          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3646,30 +3646,30 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-05</t>
+          <t>TC-COMP-09</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Analytics Screen ML Controls</t>
+          <t>Full Filter Chain Scratch Submit</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Analytics Module Browser Smoke Test</t>
+          <t>Scratch Filter Propagation Engine</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
+          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Analytics page loads with model training controls visible.</t>
-        </is>
-      </c>
-      <c r="G93" s="10" t="inlineStr">
+          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3683,30 +3683,30 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-06</t>
+          <t>TC-COMP-10</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Sprint Board All Dropdowns + Columns</t>
+          <t>Single Warehouse KPI vs Bar Chart Parity</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Sprint Board Comprehensive Module Test</t>
+          <t>Cross-Widget Calculation Parity Engine</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
+          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
-        </is>
-      </c>
-      <c r="G94" s="10" t="inlineStr">
+          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3720,30 +3720,30 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-07</t>
+          <t>TC-COMP-11</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Agent Monitor Fleet Screen</t>
+          <t>Global Submit Uses Date Parameter</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Agent Monitor Module Browser Test</t>
+          <t>Global Header Filter Engine</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
+          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
-        </is>
-      </c>
-      <c r="G95" s="10" t="inlineStr">
+          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3757,190 +3757,45 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-08</t>
+          <t>TC-COMP-12</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>MCP Explorer Screen Load</t>
+          <t>Copilot Two Warehouses Different KPI</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>MCP Explorer Module Browser Test</t>
+          <t>Copilot Warehouse Calculation Engine</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
+          <t>Discover two warehouses from API; Copilot queries must return different Cases Built totals per facility.</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
+          <t>tests\browser\test_comprehensive_module_suite.py:350: in test_copilot_two_warehouses_different_kpi
+    assert cases_a != cases_b, f"Whse {whs_a} ({cases_a}) and {whs_b} ({cases_b}) must differ"
+E   AssertionError: Whse 01 (8500) and 95 (8500) must differ
+E   assert 8500 != 8500</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="36" customHeight="1">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-09</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Full Filter Chain Scratch Submit</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>Scratch Filter Propagation Engine</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
-        </is>
-      </c>
-      <c r="G97" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="36" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-10</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>Single Warehouse KPI vs Bar Chart Parity</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>Cross-Widget Calculation Parity Engine</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
-        </is>
-      </c>
-      <c r="G98" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="36" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-11</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Global Submit Uses Date Parameter</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>Global Header Filter Engine</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
-        </is>
-      </c>
-      <c r="G99" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="36" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-12</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Two Warehouses Different KPI</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Warehouse Calculation Engine</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>Discover two warehouses from API; Copilot queries must return different Cases Built totals per facility.</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified Copilot warehouse filter returns distinct per-facility calculations from live API.</t>
-        </is>
-      </c>
-      <c r="G100" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="A61:G61"/>
     <mergeCell ref="A74:G74"/>
     <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A88:G88"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A2:G2"/>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -51,13 +51,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00166534"/>
+      <color rgb="00991B1B"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00166534"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -82,8 +82,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,8 +94,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -606,12 +606,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified agent status telemetry reports all 6 agent fleet processes active in RUNNING state.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -643,12 +643,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified system health check confirms healthy operational status and active database pool.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified data router operational status and confirmed data service readiness.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified system metadata confirming platform title AgenticOps AI and version 1.0.0.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified parameter-driven query routing executes seamlessly against requested target database.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified DEV database connection retrieves active warehouse inventory records.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified switching database reloads KPI cards, bar charts, and data tables with matching database metrics.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified AI Copilot historical date query bypasses date constraints and retrieves complete warehouse statistics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified AI Copilot search without date filter returns summary finding statements and metric totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified server-side date override executes full-dataset analysis across all historical dates.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot generates clear summary answer detailing invoice counts, cases built, and scratch quantities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified prompt '58 warehouse overview' extracts Warehouse 58 and filters chart data strictly to facility 58.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified query 'high scratch quantity' detects scratch intent and returns scratch item totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot search payload contains summary answers, applied filters, metrics, and chart data.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified submitting Copilot prompt renders summary card with matching metric counts.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot prompt updates Copilot chart, KPI cards, main bar chart, scatter plot, anomaly panel, and table.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified clicking clear button resets Copilot mode, hides banner, and restores baseline dashboard widgets.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified asking 'high scratch quantity' sets scratch filter and reloads table showing scratch rows.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified summary metrics return card data matching Cases Built, Order Qty, Invoices, and Active Warehouses.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified KPI metrics engine accepts all filter parameters and returns updated totals specific to criteria.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified dashboard loads cleanly, executes data requests, and renders 6 executive KPI cards with live values.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified submitting order date '2026-07-17' reloads KPI cards, bar chart, scatter plot, and data table with date records.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart returns data array containing warehouse labels and cases built values for active facilities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified scatter plot returns data array containing numeric order quantity and cases built coordinate points.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified analytics column service categorizes columns into numeric and categorical feature lists.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Random Forest model training fits features and returns accuracy evaluation metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Logistic Regression training fits features and returns accuracy performance metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified training both classifiers executes successfully and returns comparative performance metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified requesting invalid target column returns clear validation error message.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified querying model results before training indicates no models have been trained yet.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart calculation engine returns aggregated cases built totals for each active warehouse facility.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting custom metric calculates average metric values for each warehouse facility.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified invalid column parameter gracefully falls back to default warehouse aggregation without failure.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified scatter plot extracts valid numeric coordinate pairs for visualization.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified heatmap service calculates correlation matrix containing x, y, and correlation scores.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified distribution service calculates histogram bins with range labels and row counts.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified charts service reads SQL summary totals and returns aligned Cases Built numbers for facilities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified warehouse statistics service retrieves line items array, total count, and pagination details.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified querying warehouse statistics without date filter returns full dataset items across all dates.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified navigation bar renders AgenticOps AI branding logo and top-level navigation links.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sales analytics component renders table headers, pagination controls, and filter inputs.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified inventory risk component exports functional component with risk forecasting logic.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified warehouse service connects to PostgreSQL database and returns inventory line items and totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified data table component processes external filter properties and dynamically sets warehouse and scratch filters.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sample data service returns structured payload containing 100 row objects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified requesting 50 sample rows returns payload containing exactly 50 row objects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified dataset summary service calculates summary details containing row count and column statistics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified uploading non-CSV file reports validation error rejecting invalid file type.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified uploading valid CSV file parses rows, updates active dataset, and confirms record count.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified order date is formatted to YYYYMMDD and filtered in query returning matching order date rows.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified returned line items contain required keys: whs_num, batch_id, oerdte, cases_bld_stg, orgnl_ordr_qty_stg, and whs_scrtch_qty_stg.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified checking 'Filter Scratches' reloads data table displaying exclusively line items with scratch quantity &gt; 0.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting 'Whse 58' from dropdown reloads table displaying exclusively rows matching Warehouse 58.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified clicking pagination button fetches page 2, updating row count indicator to loaded items.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified anomaly scanner retrieves risk alert objects containing severity, title, message, and warehouse location.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified anomaly scanner outputs risk alerts with severity ratings (Critical, Warning, Info) and facility locations.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Anomaly Alert Panel renders risk cards with colored severity badges (Critical Red, Warning Amber, Info Cyan).</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified clicking 'Filter Table' on anomaly card updates table filters and displays matching Warehouse line items.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified workspace listing retrieves workspace array containing agentbuilder and project IDs.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting All Projects aggregates tasks from AgenticOps AI, AAD, and agentbuilder projects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified task objects contain exact project_name tags ('AgenticOps AI - Enterprise Control Plane', 'AI Analytics Dashboard').</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified SprintBoard.jsx renders 4 distinct Kanban columns for Backlog, To Do, In Progress, and Completed.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified changing workspace or project scope reloads sprint board tasks and updates project badges.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified AgentMonitor.jsx and AgentTaskActivityTracker.jsx render running status table and live execution stream.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Playwright browser inspects select elements and confirms dark background colors (rgb(30, 41, 59)) with crisp option styling.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified server_health.servers_healthy() reports accurate up/down status for both application ports.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified ensure_servers_running() starts missing services and browser tests proceed without connection refused errors.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified agent_watchdog.py restarts offline services without manual user intervention.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sprint_watcher_agent calls ensure_servers_running() before invoking tester_agent for unit and browser tests.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified AGENT_PICKUP_GROUPS excludes backlog and unit test test_pickup_groups_excludes_backlog passes.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
           <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3292,7 +3292,7 @@
           <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3329,7 +3329,7 @@
           <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3373,7 +3373,7 @@
           <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G85" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3410,7 +3410,7 @@
           <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="G86" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3447,7 +3447,7 @@
           <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G87" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3484,7 +3484,7 @@
           <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G88" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3521,7 +3521,7 @@
           <t>Successfully verified Analytics page loads with model training controls visible.</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3558,7 +3558,7 @@
           <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="G90" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3595,7 +3595,7 @@
           <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="G91" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3632,7 +3632,7 @@
           <t>Successfully verified MCP Explorer page loads with server registry content.</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3669,7 +3669,7 @@
           <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G93" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3706,7 +3706,7 @@
           <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3743,7 +3743,7 @@
           <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3777,13 +3777,14 @@
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>tests\browser\test_comprehensive_module_suite.py:350: in test_copilot_two_warehouses_different_kpi
-    assert cases_a != cases_b, f"Whse {whs_a} ({cases_a}) and {whs_b} ({cases_b}) must differ"
-E   AssertionError: Whse 01 (8500) and 95 (8500) must differ
-E   assert 8500 != 8500</t>
-        </is>
-      </c>
-      <c r="G96" s="10" t="inlineStr">
+          <t>tests\browser\test_comprehensive_module_suite.py:353: in test_copilot_two_warehouses_different_kpi
+    assert_cases_aligned(cases_a, exp_a)
+tests\browser\calculation_verifier.py:114: in assert_cases_aligned
+    assert diff &lt;= allowed, (
+E   AssertionError: Cases built mismatch: API=0 UI=8,500 (diff=8,500)</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -51,13 +51,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00166534"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00166534"/>
+      <color rgb="00991B1B"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -82,8 +82,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,8 +94,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -606,12 +606,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified agent status telemetry reports all 6 agent fleet processes active in RUNNING state.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -643,12 +643,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified system health check confirms healthy operational status and active database pool.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified data router operational status and confirmed data service readiness.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified system metadata confirming platform title AgenticOps AI and version 1.0.0.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified parameter-driven query routing executes seamlessly against requested target database.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified DEV database connection retrieves active warehouse inventory records.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
+          <t>Successfully verified switching database reloads KPI cards, bar charts, and data tables with matching database metrics.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AI Copilot historical date query bypasses date constraints and retrieves complete warehouse statistics.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AI Copilot search without date filter returns summary finding statements and metric totals.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified server-side date override executes full-dataset analysis across all historical dates.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot generates clear summary answer detailing invoice counts, cases built, and scratch quantities.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified prompt '58 warehouse overview' extracts Warehouse 58 and filters chart data strictly to facility 58.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified query 'high scratch quantity' detects scratch intent and returns scratch item totals.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot search payload contains summary answers, applied filters, metrics, and chart data.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified submitting Copilot prompt renders summary card with matching metric counts.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Copilot prompt updates Copilot chart, KPI cards, main bar chart, scatter plot, anomaly panel, and table.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking clear button resets Copilot mode, hides banner, and restores baseline dashboard widgets.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified asking 'high scratch quantity' sets scratch filter and reloads table showing scratch rows.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified summary metrics return card data matching Cases Built, Order Qty, Invoices, and Active Warehouses.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified KPI metrics engine accepts all filter parameters and returns updated totals specific to criteria.</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified dashboard loads cleanly, executes data requests, and renders 6 executive KPI cards with live values.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified submitting order date '2026-07-17' reloads KPI cards, bar chart, scatter plot, and data table with date records.</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified bar chart returns data array containing warehouse labels and cases built values for active facilities.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified scatter plot returns data array containing numeric order quantity and cases built coordinate points.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified analytics column service categorizes columns into numeric and categorical feature lists.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Random Forest model training fits features and returns accuracy evaluation metrics.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Logistic Regression training fits features and returns accuracy performance metrics.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified training both classifiers executes successfully and returns comparative performance metrics.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified requesting invalid target column returns clear validation error message.</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified querying model results before training indicates no models have been trained yet.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified bar chart calculation engine returns aggregated cases built totals for each active warehouse facility.</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting custom metric calculates average metric values for each warehouse facility.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified invalid column parameter gracefully falls back to default warehouse aggregation without failure.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified scatter plot extracts valid numeric coordinate pairs for visualization.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified heatmap service calculates correlation matrix containing x, y, and correlation scores.</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified distribution service calculates histogram bins with range labels and row counts.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified charts service reads SQL summary totals and returns aligned Cases Built numbers for facilities.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified warehouse statistics service retrieves line items array, total count, and pagination details.</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified querying warehouse statistics without date filter returns full dataset items across all dates.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified navigation bar renders AgenticOps AI branding logo and top-level navigation links.</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sales analytics component renders table headers, pagination controls, and filter inputs.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified inventory risk component exports functional component with risk forecasting logic.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified warehouse service connects to PostgreSQL database and returns inventory line items and totals.</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified data table component processes external filter properties and dynamically sets warehouse and scratch filters.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sample data service returns structured payload containing 100 row objects.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified requesting 50 sample rows returns payload containing exactly 50 row objects.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified dataset summary service calculates summary details containing row count and column statistics.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified uploading non-CSV file reports validation error rejecting invalid file type.</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified uploading valid CSV file parses rows, updates active dataset, and confirms record count.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified order date is formatted to YYYYMMDD and filtered in query returning matching order date rows.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified returned line items contain required keys: whs_num, batch_id, oerdte, cases_bld_stg, orgnl_ordr_qty_stg, and whs_scrtch_qty_stg.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified checking 'Filter Scratches' reloads data table displaying exclusively line items with scratch quantity &gt; 0.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting 'Whse 58' from dropdown reloads table displaying exclusively rows matching Warehouse 58.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking pagination button fetches page 2, updating row count indicator to loaded items.</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified anomaly scanner retrieves risk alert objects containing severity, title, message, and warehouse location.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified anomaly scanner outputs risk alerts with severity ratings (Critical, Warning, Info) and facility locations.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Anomaly Alert Panel renders risk cards with colored severity badges (Critical Red, Warning Amber, Info Cyan).</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified clicking 'Filter Table' on anomaly card updates table filters and displays matching Warehouse line items.</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified workspace listing retrieves workspace array containing agentbuilder and project IDs.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified selecting All Projects aggregates tasks from AgenticOps AI, AAD, and agentbuilder projects.</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified task objects contain exact project_name tags ('AgenticOps AI - Enterprise Control Plane', 'AI Analytics Dashboard').</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified SprintBoard.jsx renders 4 distinct Kanban columns for Backlog, To Do, In Progress, and Completed.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified changing workspace or project scope reloads sprint board tasks and updates project badges.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AgentMonitor.jsx and AgentTaskActivityTracker.jsx render running status table and live execution stream.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified Playwright browser inspects select elements and confirms dark background colors (rgb(30, 41, 59)) with crisp option styling.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified server_health.servers_healthy() reports accurate up/down status for both application ports.</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified ensure_servers_running() starts missing services and browser tests proceed without connection refused errors.</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified agent_watchdog.py restarts offline services without manual user intervention.</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified sprint_watcher_agent calls ensure_servers_running() before invoking tester_agent for unit and browser tests.</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3208,36 +3208,36 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Browser test suite did not pass completely on last run.</t>
+          <t>Successfully verified AGENT_PICKUP_GROUPS excludes backlog and unit test test_pickup_groups_excludes_backlog passes.</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  📋 Sprint Task: Add Aditional Features</t>
+          <t xml:space="preserve">  📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Add Aditional Features</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-B1CE165D-SMOKE</t>
+          <t>TC-TASK-TEST-TAS-SMOKE</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Dashboard smoke after sprint task: Add Aditional Features</t>
+          <t>Dashboard smoke after sprint task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3247,133 +3247,163 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>After implementing the sprint task 'Add Aditional Features', the main dashboard loads with KPI cards and global header controls working.</t>
+          <t>After implementing the sprint task 'Sprint Board Browser Navigation', the main dashboard loads with KPI cards and global header controls working.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Awaiting browser test execution for this sprint task case.</t>
+          <t>Successfully verified in browser: After implementing the sprint task 'Sprint Board Browser Navigation', the main dashboard loads with KPI cards and global</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Add Aditional Features</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-B1CE165D-AGENTS</t>
+          <t>TC-TASK-TEST-TAS-SPRINT-UI</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Agent status telemetry visible in sidebar</t>
+          <t>Sprint board page loads with workspace and project selectors</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Agent Fleet Monitoring Verification</t>
+          <t>Sprint Board Browser Verification</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+          <t>The Sprint Board page displays workspace and project dropdowns and kanban column headers.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Awaiting browser test execution for this sprint task case.</t>
+          <t>Successfully verified in browser: The Sprint Board page displays workspace and project dropdowns and kanban column headers.</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Add Aditional Features</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-B1CE165D-UPTIME</t>
+          <t>TC-TASK-TEST-TAS-COPILOT</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Application servers respond for browser testing</t>
+          <t>AI Data Copilot accepts prompts and shows results</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Application Uptime Verification</t>
+          <t>AI Data Copilot Sprint Task Verification</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
+          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Awaiting browser test execution for this sprint task case.</t>
+          <t>Successfully verified in browser: The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>TC-TASK-TEST-TAS-TABLE</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse sales table loads with data rows</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse Analytics Table Verification</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified in browser: Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-01</t>
+          <t>TC-TASK-TEST-TAS-HEADER</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Dashboard Date+DB Submit KPI Alignment</t>
+          <t>Global header controls and clear filter work</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Comprehensive Dashboard Filter Engine</t>
+          <t>Header Controls Sprint Task Verification</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
+          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
+          <t>Successfully verified in browser: Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3382,35 +3412,35 @@
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-02</t>
+          <t>TC-TASK-TEST-TAS-AGENTS</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Warehouse Filter Bar Chart Calculation</t>
+          <t>Agent status telemetry visible in sidebar</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Warehouse Bar Chart Calculation Verifier</t>
+          <t>Agent Fleet Monitoring Verification</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
+          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr">
+          <t>Successfully verified in browser: The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3419,74 +3449,44 @@
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-03</t>
+          <t>TC-TASK-TEST-TAS-UPTIME</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Table Summary Cards API Alignment</t>
+          <t>Application servers respond for browser testing</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Warehouse Table Summary Calculation Engine</t>
+          <t>Application Uptime Verification</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
+          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
-        </is>
-      </c>
-      <c r="G87" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="36" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-04</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Search Without Date Parameter</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Date-Agnostic Search Engine</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
-        </is>
-      </c>
-      <c r="G88" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Successfully verified in browser: The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
     </row>
@@ -3498,30 +3498,30 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-05</t>
+          <t>TC-COMP-01</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Analytics Screen ML Controls</t>
+          <t>Dashboard Date+DB Submit KPI Alignment</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Analytics Module Browser Smoke Test</t>
+          <t>Comprehensive Dashboard Filter Engine</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
+          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Analytics page loads with model training controls visible.</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
+          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3535,30 +3535,30 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-06</t>
+          <t>TC-COMP-02</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Sprint Board All Dropdowns + Columns</t>
+          <t>Warehouse Filter Bar Chart Calculation</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Sprint Board Comprehensive Module Test</t>
+          <t>Warehouse Bar Chart Calculation Verifier</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
+          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
+          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3572,30 +3572,30 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-07</t>
+          <t>TC-COMP-03</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Agent Monitor Fleet Screen</t>
+          <t>Table Summary Cards API Alignment</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Agent Monitor Module Browser Test</t>
+          <t>Warehouse Table Summary Calculation Engine</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
+          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
-        </is>
-      </c>
-      <c r="G91" s="10" t="inlineStr">
+          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3609,30 +3609,30 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-08</t>
+          <t>TC-COMP-04</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>MCP Explorer Screen Load</t>
+          <t>Copilot Search Without Date Parameter</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>MCP Explorer Module Browser Test</t>
+          <t>Copilot Date-Agnostic Search Engine</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
+          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
-        </is>
-      </c>
-      <c r="G92" s="10" t="inlineStr">
+          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3646,30 +3646,30 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-09</t>
+          <t>TC-COMP-05</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Full Filter Chain Scratch Submit</t>
+          <t>Analytics Screen ML Controls</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Scratch Filter Propagation Engine</t>
+          <t>Analytics Module Browser Smoke Test</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
+          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
-        </is>
-      </c>
-      <c r="G93" s="10" t="inlineStr">
+          <t>Successfully verified Analytics page loads with model training controls visible.</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3683,30 +3683,30 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>TC-COMP-10</t>
+          <t>TC-COMP-06</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Single Warehouse KPI vs Bar Chart Parity</t>
+          <t>Sprint Board All Dropdowns + Columns</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Cross-Widget Calculation Parity Engine</t>
+          <t>Sprint Board Comprehensive Module Test</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
+          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
-        </is>
-      </c>
-      <c r="G94" s="10" t="inlineStr">
+          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3720,30 +3720,30 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>TC-COMP-11</t>
+          <t>TC-COMP-07</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Global Submit Uses Date Parameter</t>
+          <t>Agent Monitor Fleet Screen</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Global Header Filter Engine</t>
+          <t>Agent Monitor Module Browser Test</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
+          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
-        </is>
-      </c>
-      <c r="G95" s="10" t="inlineStr">
+          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3757,34 +3757,181 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
+          <t>TC-COMP-08</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Screen Load</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Module Browser Test</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-09</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Full Filter Chain Scratch Submit</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Scratch Filter Propagation Engine</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-10</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Single Warehouse KPI vs Bar Chart Parity</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>Cross-Widget Calculation Parity Engine</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-11</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Global Submit Uses Date Parameter</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Global Header Filter Engine</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
           <t>TC-COMP-12</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C100" s="9" t="inlineStr">
         <is>
           <t>Copilot Two Warehouses Different KPI</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="D100" s="9" t="inlineStr">
         <is>
           <t>Copilot Warehouse Calculation Engine</t>
         </is>
       </c>
-      <c r="E96" s="9" t="inlineStr">
+      <c r="E100" s="9" t="inlineStr">
         <is>
           <t>Discover two warehouses from API; Copilot queries must return different Cases Built totals per facility.</t>
         </is>
       </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>tests\browser\test_comprehensive_module_suite.py:353: in test_copilot_two_warehouses_different_kpi
-    assert_cases_aligned(cases_a, exp_a)
-tests\browser\calculation_verifier.py:114: in assert_cases_aligned
-    assert diff &lt;= allowed, (
-E   AssertionError: Cases built mismatch: API=0 UI=8,500 (diff=8,500)</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>tests\browser\test_comprehensive_module_suite.py:350: in test_copilot_two_warehouses_different_kpi
+    assert cases_a != cases_b, f"Whse {whs_a} ({cases_a}) and {whs_b} ({cases_b}) must differ"
+E   AssertionError: Whse 01 (8500) and 95 (8500) must differ
+E   assert 8500 != 8500</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3792,11 +3939,11 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="A61:G61"/>
     <mergeCell ref="A74:G74"/>
     <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A88:G88"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A2:G2"/>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -51,13 +51,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00166534"/>
+      <color rgb="00991B1B"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00166534"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -82,8 +82,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,8 +94,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -606,12 +606,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified agent status telemetry reports all 6 agent fleet processes active in RUNNING state.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -643,12 +643,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified system health check confirms healthy operational status and active database pool.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified data router operational status and confirmed data service readiness.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified system metadata confirming platform title AgenticOps AI and version 1.0.0.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified parameter-driven query routing executes seamlessly against requested target database.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified DEV database connection retrieves active warehouse inventory records.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified switching database reloads KPI cards, bar charts, and data tables with matching database metrics.</t>
+          <t>Regression detected — full test suite did not pass on last autonomous run.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified AI Copilot historical date query bypasses date constraints and retrieves complete warehouse statistics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified AI Copilot search without date filter returns summary finding statements and metric totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified server-side date override executes full-dataset analysis across all historical dates.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot generates clear summary answer detailing invoice counts, cases built, and scratch quantities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified prompt '58 warehouse overview' extracts Warehouse 58 and filters chart data strictly to facility 58.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified query 'high scratch quantity' detects scratch intent and returns scratch item totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot search payload contains summary answers, applied filters, metrics, and chart data.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified submitting Copilot prompt renders summary card with matching metric counts.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Copilot prompt updates Copilot chart, KPI cards, main bar chart, scatter plot, anomaly panel, and table.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified clicking clear button resets Copilot mode, hides banner, and restores baseline dashboard widgets.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified asking 'high scratch quantity' sets scratch filter and reloads table showing scratch rows.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified summary metrics return card data matching Cases Built, Order Qty, Invoices, and Active Warehouses.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified KPI metrics engine accepts all filter parameters and returns updated totals specific to criteria.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified dashboard loads cleanly, executes data requests, and renders 6 executive KPI cards with live values.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified submitting order date '2026-07-17' reloads KPI cards, bar chart, scatter plot, and data table with date records.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart returns data array containing warehouse labels and cases built values for active facilities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified scatter plot returns data array containing numeric order quantity and cases built coordinate points.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified analytics column service categorizes columns into numeric and categorical feature lists.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified Random Forest model training fits features and returns accuracy evaluation metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Logistic Regression training fits features and returns accuracy performance metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified training both classifiers executes successfully and returns comparative performance metrics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified requesting invalid target column returns clear validation error message.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified querying model results before training indicates no models have been trained yet.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified bar chart calculation engine returns aggregated cases built totals for each active warehouse facility.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting custom metric calculates average metric values for each warehouse facility.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified invalid column parameter gracefully falls back to default warehouse aggregation without failure.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified scatter plot extracts valid numeric coordinate pairs for visualization.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified heatmap service calculates correlation matrix containing x, y, and correlation scores.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified distribution service calculates histogram bins with range labels and row counts.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified charts service reads SQL summary totals and returns aligned Cases Built numbers for facilities.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified warehouse statistics service retrieves line items array, total count, and pagination details.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified querying warehouse statistics without date filter returns full dataset items across all dates.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified navigation bar renders AgenticOps AI branding logo and top-level navigation links.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sales analytics component renders table headers, pagination controls, and filter inputs.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified inventory risk component exports functional component with risk forecasting logic.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified warehouse service connects to PostgreSQL database and returns inventory line items and totals.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified data table component processes external filter properties and dynamically sets warehouse and scratch filters.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sample data service returns structured payload containing 100 row objects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified requesting 50 sample rows returns payload containing exactly 50 row objects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified dataset summary service calculates summary details containing row count and column statistics.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified uploading non-CSV file reports validation error rejecting invalid file type.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified uploading valid CSV file parses rows, updates active dataset, and confirms record count.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified order date is formatted to YYYYMMDD and filtered in query returning matching order date rows.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified returned line items contain required keys: whs_num, batch_id, oerdte, cases_bld_stg, orgnl_ordr_qty_stg, and whs_scrtch_qty_stg.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified checking 'Filter Scratches' reloads data table displaying exclusively line items with scratch quantity &gt; 0.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting 'Whse 58' from dropdown reloads table displaying exclusively rows matching Warehouse 58.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified clicking pagination button fetches page 2, updating row count indicator to loaded items.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified anomaly scanner retrieves risk alert objects containing severity, title, message, and warehouse location.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified anomaly scanner outputs risk alerts with severity ratings (Critical, Warning, Info) and facility locations.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Anomaly Alert Panel renders risk cards with colored severity badges (Critical Red, Warning Amber, Info Cyan).</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified clicking 'Filter Table' on anomaly card updates table filters and displays matching Warehouse line items.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified workspace listing retrieves workspace array containing agentbuilder and project IDs.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified selecting All Projects aggregates tasks from AgenticOps AI, AAD, and agentbuilder projects.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified task objects contain exact project_name tags ('AgenticOps AI - Enterprise Control Plane', 'AI Analytics Dashboard').</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified SprintBoard.jsx renders 4 distinct Kanban columns for Backlog, To Do, In Progress, and Completed.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified changing workspace or project scope reloads sprint board tasks and updates project badges.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified AgentMonitor.jsx and AgentTaskActivityTracker.jsx render running status table and live execution stream.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified Playwright browser inspects select elements and confirms dark background colors (rgb(30, 41, 59)) with crisp option styling.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified server_health.servers_healthy() reports accurate up/down status for both application ports.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified ensure_servers_running() starts missing services and browser tests proceed without connection refused errors.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified agent_watchdog.py restarts offline services without manual user intervention.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified sprint_watcher_agent calls ensure_servers_running() before invoking tester_agent for unit and browser tests.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3208,36 +3208,36 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified AGENT_PICKUP_GROUPS excludes backlog and unit test test_pickup_groups_excludes_backlog passes.</t>
+          <t>Browser test suite did not pass completely on last run.</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t xml:space="preserve">  📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
         </is>
       </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-SMOKE</t>
+          <t>TC-TASK-7945706C-SMOKE</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Dashboard smoke after sprint task: Sprint Board Browser Navigation</t>
+          <t>Dashboard smoke after sprint task: Train the uploaded the csv file and show the analytics</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3247,683 +3247,646 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>After implementing the sprint task 'Sprint Board Browser Navigation', the main dashboard loads with KPI cards and global header controls working.</t>
+          <t>After implementing the sprint task 'Train the uploaded the csv file and show the analytics', the main dashboard loads with KPI cards and global header controls working.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: After implementing the sprint task 'Sprint Board Browser Navigation', the main dashboard loads with KPI cards and global</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-SPRINT-UI</t>
+          <t>TC-TASK-7945706C-COPILOT</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Sprint board page loads with workspace and project selectors</t>
+          <t>AI Data Copilot accepts prompts and shows results</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Sprint Board Browser Verification</t>
+          <t>AI Data Copilot Sprint Task Verification</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>The Sprint Board page displays workspace and project dropdowns and kanban column headers.</t>
+          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: The Sprint Board page displays workspace and project dropdowns and kanban column headers.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-COPILOT</t>
+          <t>TC-TASK-7945706C-TABLE</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>AI Data Copilot accepts prompts and shows results</t>
+          <t>Warehouse sales table loads with data rows</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>AI Data Copilot Sprint Task Verification</t>
+          <t>Warehouse Analytics Table Verification</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
+          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-TABLE</t>
+          <t>TC-TASK-7945706C-HEADER</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Warehouse sales table loads with data rows</t>
+          <t>Global header controls and clear filter work</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Warehouse Analytics Table Verification</t>
+          <t>Header Controls Sprint Task Verification</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-HEADER</t>
+          <t>TC-TASK-7945706C-AGENTS</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Global header controls and clear filter work</t>
+          <t>Agent status telemetry visible in sidebar</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Header Controls Sprint Task Verification</t>
+          <t>Agent Fleet Monitoring Verification</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
+          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
+          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-TEST-TAS-AGENTS</t>
+          <t>TC-TASK-7945706C-UPTIME</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Agent status telemetry visible in sidebar</t>
+          <t>Application servers respond for browser testing</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Agent Fleet Monitoring Verification</t>
+          <t>Application Uptime Verification</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Successfully verified in browser: The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+          <t>Awaiting browser test execution for this sprint task case.</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-01</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard Date+DB Submit KPI Alignment</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Comprehensive Dashboard Filter Engine</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="36" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>📋 Sprint Task: Sprint Board Browser Navigation</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>TC-TASK-TEST-TAS-UPTIME</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>Application servers respond for browser testing</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>Application Uptime Verification</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified in browser: The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-02</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse Filter Bar Chart Calculation</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse Bar Chart Calculation Verifier</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="36" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-01</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>Dashboard Date+DB Submit KPI Alignment</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>Comprehensive Dashboard Filter Engine</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-03</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Table Summary Cards API Alignment</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Warehouse Table Summary Calculation Engine</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="36" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
+    <row r="91" ht="36" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-02</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>Warehouse Filter Bar Chart Calculation</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>Warehouse Bar Chart Calculation Verifier</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-04</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Search Without Date Parameter</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Date-Agnostic Search Engine</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="36" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
+    <row r="92" ht="36" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-03</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>Table Summary Cards API Alignment</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>Warehouse Table Summary Calculation Engine</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-05</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Analytics Screen ML Controls</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Analytics Module Browser Smoke Test</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified Analytics page loads with model training controls visible.</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="36" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
+    <row r="93" ht="36" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-04</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Search Without Date Parameter</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Date-Agnostic Search Engine</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-06</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Board All Dropdowns + Columns</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Board Comprehensive Module Test</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
+    <row r="94" ht="36" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-05</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Analytics Screen ML Controls</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Analytics Module Browser Smoke Test</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified Analytics page loads with model training controls visible.</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-07</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Agent Monitor Fleet Screen</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Agent Monitor Module Browser Test</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="36" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
+    <row r="95" ht="36" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-06</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>Sprint Board All Dropdowns + Columns</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>Sprint Board Comprehensive Module Test</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-08</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Screen Load</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Module Browser Test</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="36" customHeight="1">
-      <c r="A95" s="3" t="inlineStr">
+    <row r="96" ht="36" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-07</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Agent Monitor Fleet Screen</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>Agent Monitor Module Browser Test</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-09</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Full Filter Chain Scratch Submit</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Scratch Filter Propagation Engine</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="36" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
+    <row r="97" ht="36" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-08</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>MCP Explorer Screen Load</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>MCP Explorer Module Browser Test</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-10</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>Single Warehouse KPI vs Bar Chart Parity</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Cross-Widget Calculation Parity Engine</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="36" customHeight="1">
-      <c r="A97" s="3" t="inlineStr">
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-09</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Full Filter Chain Scratch Submit</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>Scratch Filter Propagation Engine</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-11</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Global Submit Uses Date Parameter</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Global Header Filter Engine</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="36" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-10</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>Single Warehouse KPI vs Bar Chart Parity</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>Cross-Widget Calculation Parity Engine</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="36" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-11</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Global Submit Uses Date Parameter</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>Global Header Filter Engine</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="36" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>TC-COMP-12</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>Copilot Two Warehouses Different KPI</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
+      <c r="D99" s="9" t="inlineStr">
         <is>
           <t>Copilot Warehouse Calculation Engine</t>
         </is>
       </c>
-      <c r="E100" s="9" t="inlineStr">
+      <c r="E99" s="9" t="inlineStr">
         <is>
           <t>Discover two warehouses from API; Copilot queries must return different Cases Built totals per facility.</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr">
+      <c r="F99" s="9" t="inlineStr">
         <is>
           <t>tests\browser\test_comprehensive_module_suite.py:350: in test_copilot_two_warehouses_different_kpi
     assert cases_a != cases_b, f"Whse {whs_a} ({cases_a}) and {whs_b} ({cases_b}) must differ"
@@ -3931,7 +3894,7 @@
 E   assert 8500 != 8500</t>
         </is>
       </c>
-      <c r="G100" s="10" t="inlineStr">
+      <c r="G99" s="6" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3943,9 +3906,9 @@
     <mergeCell ref="A61:G61"/>
     <mergeCell ref="A74:G74"/>
     <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A88:G88"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A87:G87"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A10:G10"/>

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-7945706C-SMOKE</t>
+          <t>TC-TASK-CFAF3D1D-SMOKE</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-7945706C-COPILOT</t>
+          <t>TC-TASK-CFAF3D1D-COPILOT</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-7945706C-TABLE</t>
+          <t>TC-TASK-CFAF3D1D-TABLE</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-7945706C-HEADER</t>
+          <t>TC-TASK-CFAF3D1D-HEADER</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-7945706C-AGENTS</t>
+          <t>TC-TASK-CFAF3D1D-AGENTS</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-7945706C-UPTIME</t>
+          <t>TC-TASK-CFAF3D1D-UPTIME</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">

--- a/tests/TEST_CASES.xlsx
+++ b/tests/TEST_CASES.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3220,24 +3220,24 @@
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
+          <t xml:space="preserve">  📋 Sprint Task: Training the csv data</t>
         </is>
       </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
+          <t>📋 Sprint Task: Training the csv data</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-CFAF3D1D-SMOKE</t>
+          <t>TC-TASK-1BBBDF8A-SMOKE</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Dashboard smoke after sprint task: Train the uploaded the csv file and show the analytics</t>
+          <t>Dashboard smoke after sprint task: Training the csv data</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>After implementing the sprint task 'Train the uploaded the csv file and show the analytics', the main dashboard loads with KPI cards and global header controls working.</t>
+          <t>After implementing the sprint task 'Training the csv data', the main dashboard loads with KPI cards and global header controls working.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -3264,27 +3264,27 @@
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
+          <t>📋 Sprint Task: Training the csv data</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-CFAF3D1D-COPILOT</t>
+          <t>TC-TASK-1BBBDF8A-SPRINT-UI</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>AI Data Copilot accepts prompts and shows results</t>
+          <t>Sprint board page loads with workspace and project selectors</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>AI Data Copilot Sprint Task Verification</t>
+          <t>Sprint Board Browser Verification</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
+          <t>The Sprint Board page displays workspace and project dropdowns and kanban column headers.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
@@ -3301,27 +3301,27 @@
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
+          <t>📋 Sprint Task: Training the csv data</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-CFAF3D1D-TABLE</t>
+          <t>TC-TASK-1BBBDF8A-COPILOT</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Warehouse sales table loads with data rows</t>
+          <t>AI Data Copilot accepts prompts and shows results</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Warehouse Analytics Table Verification</t>
+          <t>AI Data Copilot Sprint Task Verification</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
+          <t>The AI Data Copilot search box and Ask AI control are visible and a quick insight pill triggers an analysis result card.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -3338,27 +3338,27 @@
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
+          <t>📋 Sprint Task: Training the csv data</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>TC-TASK-CFAF3D1D-HEADER</t>
+          <t>TC-TASK-1BBBDF8A-TABLE</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Global header controls and clear filter work</t>
+          <t>Warehouse sales table loads with data rows</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Header Controls Sprint Task Verification</t>
+          <t>Warehouse Analytics Table Verification</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
+          <t>Selecting the development database and submitting loads the warehouse item table with visible rows.</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
@@ -3375,27 +3375,27 @@
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
+          <t>📋 Sprint Task: Training the csv data</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>TC-TASK-CFAF3D1D-AGENTS</t>
+          <t>TC-TASK-1BBBDF8A-HEADER</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Agent status telemetry visible in sidebar</t>
+          <t>Global header controls and clear filter work</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Agent Fleet Monitoring Verification</t>
+          <t>Header Controls Sprint Task Verification</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>The dashboard sidebar shows agent status information for the autonomous agent fleet.</t>
+          <t>Global date picker, database selector, submit button, and clear filter control are visible on the dashboard.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -3409,79 +3409,79 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="36" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>📋 Sprint Task: Train the uploaded the csv file and show the analy</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>TC-TASK-CFAF3D1D-UPTIME</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>Application servers respond for browser testing</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>Application Uptime Verification</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>The dashboard and sprint board pages load in the browser confirming frontend and backend services are running.</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>Awaiting browser test execution for this sprint task case.</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
     </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-01</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard Date+DB Submit KPI Alignment</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Comprehensive Dashboard Filter Engine</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
     <row r="88" ht="36" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-01</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>Dashboard Date+DB Submit KPI Alignment</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>Comprehensive Dashboard Filter Engine</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>Select global order date and target DB, click Submit, and verify KPI Cases Built matches backend API totals.</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified KPI Cases Built on dashboard matches /api/charts/kpi for same date and database.</t>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-02</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse Filter Bar Chart Calculation</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Warehouse Bar Chart Calculation Verifier</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
@@ -3491,34 +3491,34 @@
       </c>
     </row>
     <row r="89" ht="36" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-02</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>Warehouse Filter Bar Chart Calculation</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>Warehouse Bar Chart Calculation Verifier</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>Select date and warehouse facility, Submit, and verify bar chart aggregated cases match API warehouse_totals.</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified bar chart total cases align with SQL warehouse_totals for selected facility.</t>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-03</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Table Summary Cards API Alignment</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Warehouse Table Summary Calculation Engine</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -3528,34 +3528,34 @@
       </c>
     </row>
     <row r="90" ht="36" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-03</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Table Summary Cards API Alignment</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Warehouse Table Summary Calculation Engine</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Verify warehouse table summary cards (Cases Built, Order Qty) match /api/warehouse/statistics summary.</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified table summary cards match backend SQL aggregate summary for selected filters.</t>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-04</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Search Without Date Parameter</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>Copilot Date-Agnostic Search Engine</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -3565,34 +3565,34 @@
       </c>
     </row>
     <row r="91" ht="36" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-04</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Search Without Date Parameter</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>Copilot Date-Agnostic Search Engine</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>Set global date and Submit, then run Copilot query; verify copilot sends oerdte='' and KPI matches no-date API.</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified Copilot ignores global date and searches across all available dates.</t>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-05</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Analytics Screen ML Controls</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Analytics Module Browser Smoke Test</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified Analytics page loads with model training controls visible.</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
@@ -3602,34 +3602,34 @@
       </c>
     </row>
     <row r="92" ht="36" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-05</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>Analytics Screen ML Controls</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>Analytics Module Browser Smoke Test</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>Navigate to /analytics and verify ML upload and train controls render.</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified Analytics page loads with model training controls visible.</t>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-06</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Board All Dropdowns + Columns</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Board Comprehensive Module Test</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
@@ -3639,34 +3639,34 @@
       </c>
     </row>
     <row r="93" ht="36" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-06</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>Sprint Board All Dropdowns + Columns</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>Sprint Board Comprehensive Module Test</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>Select workspace and project dropdowns on Sprint Board and verify all 4 kanban columns render.</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified Sprint Board workspace/project selectors and Backlog/To Do/In Progress/Completed columns.</t>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-07</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Agent Monitor Fleet Screen</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Agent Monitor Module Browser Test</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -3676,34 +3676,34 @@
       </c>
     </row>
     <row r="94" ht="36" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-07</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Agent Monitor Fleet Screen</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>Agent Monitor Module Browser Test</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>Navigate to /agents and verify agent fleet cards and monitor panels load.</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified Agent Monitor displays fleet agent status cards.</t>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-08</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Screen Load</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>MCP Explorer Module Browser Test</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
@@ -3713,34 +3713,34 @@
       </c>
     </row>
     <row r="95" ht="36" customHeight="1">
-      <c r="A95" s="7" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-08</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>MCP Explorer Screen Load</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>MCP Explorer Module Browser Test</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>Navigate to /mcp and verify MCP server registry page loads.</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified MCP Explorer page loads with server registry content.</t>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-09</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Full Filter Chain Scratch Submit</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Scratch Filter Propagation Engine</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -3750,34 +3750,34 @@
       </c>
     </row>
     <row r="96" ht="36" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-09</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Full Filter Chain Scratch Submit</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>Scratch Filter Propagation Engine</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>Apply date, DB, and scratch filter; verify scratch KPI reflects only_scratches API parameter.</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified scratch filter propagates to KPI API with only_scratches=true.</t>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>TC-COMP-10</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Single Warehouse KPI vs Bar Chart Parity</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>Cross-Widget Calculation Parity Engine</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -3787,34 +3787,34 @@
       </c>
     </row>
     <row r="97" ht="36" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>TC-COMP-10</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>Single Warehouse KPI vs Bar Chart Parity</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>Cross-Widget Calculation Parity Engine</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>With one warehouse selected, KPI Cases Built must equal bar chart total cases.</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>Successfully verified KPI Cases Built equals bar chart sum for single-warehouse filter.</t>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>TC-COMP-11</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Global Submit Uses Date Parameter</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Global Header Filter Engine</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -3824,69 +3824,32 @@
       </c>
     </row>
     <row r="98" ht="36" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>TC-COMP-11</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>Global Submit Uses Date Parameter</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>Global Header Filter Engine</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>Global date + Submit must send oerdte to KPI API and align calculations with dated API response.</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>Successfully verified global Submit applies order date and KPI matches dated API totals.</t>
-        </is>
-      </c>
-      <c r="G98" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="36" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>🧪 Comprehensive Module Browser Tests (All Fields + Calculation Verification)</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>TC-COMP-12</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C98" s="9" t="inlineStr">
         <is>
           <t>Copilot Two Warehouses Different KPI</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
+      <c r="D98" s="9" t="inlineStr">
         <is>
           <t>Copilot Warehouse Calculation Engine</t>
         </is>
       </c>
-      <c r="E99" s="9" t="inlineStr">
+      <c r="E98" s="9" t="inlineStr">
         <is>
           <t>Discover two warehouses from API; Copilot queries must return different Cases Built totals per facility.</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
+      <c r="F98" s="9" t="inlineStr">
         <is>
           <t>tests\browser\test_comprehensive_module_suite.py:350: in test_copilot_two_warehouses_different_kpi
     assert cases_a != cases_b, f"Whse {whs_a} ({cases_a}) and {whs_b} ({cases_b}) must differ"
@@ -3894,7 +3857,7 @@
 E   assert 8500 != 8500</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="G98" s="6" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3908,8 +3871,8 @@
     <mergeCell ref="A80:G80"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A87:G87"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A86:G86"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
